--- a/output/yearly_surface_area_iteration_31_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_31_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497631484804</v>
+        <v>10.84497634069633</v>
       </c>
       <c r="C21" t="n">
-        <v>37.7890718813945</v>
+        <v>37.7890719714623</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.382922662385262</v>
+        <v>5.506622873120359</v>
       </c>
       <c r="C2" t="n">
-        <v>8.273187903687871</v>
+        <v>6.137886646951058</v>
       </c>
       <c r="D2" t="n">
-        <v>21.94991517155019</v>
+        <v>36.70165617556276</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.45547418150829</v>
+        <v>17.20021977840412</v>
       </c>
       <c r="C3" t="n">
-        <v>31.25393816469721</v>
+        <v>28.04362317181014</v>
       </c>
       <c r="D3" t="n">
-        <v>60.24003913258429</v>
+        <v>94.58648256565895</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.95785126864217</v>
+        <v>36.53966780436203</v>
       </c>
       <c r="C4" t="n">
-        <v>86.93964969728053</v>
+        <v>76.4104055692335</v>
       </c>
       <c r="D4" t="n">
-        <v>89.26246476552849</v>
+        <v>109.491376211534</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.17802479630072</v>
+        <v>44.08047192068179</v>
       </c>
       <c r="C5" t="n">
-        <v>133.0022702328367</v>
+        <v>113.3918598405066</v>
       </c>
       <c r="D5" t="n">
-        <v>66.58703804053992</v>
+        <v>77.45989386507335</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.6290068454485</v>
+        <v>37.99756314516856</v>
       </c>
       <c r="C6" t="n">
-        <v>146.8782922846611</v>
+        <v>116.7700536908199</v>
       </c>
       <c r="D6" t="n">
-        <v>46.16864928761476</v>
+        <v>50.636583089642</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.81112889235289</v>
+        <v>24.43373686329462</v>
       </c>
       <c r="C7" t="n">
-        <v>131.3912222501676</v>
+        <v>110.0117024947848</v>
       </c>
       <c r="D7" t="n">
-        <v>38.5669768136317</v>
+        <v>39.58504918293564</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.85246010692249</v>
+        <v>12.76762889372977</v>
       </c>
       <c r="C8" t="n">
-        <v>91.96030745679872</v>
+        <v>73.76852249710534</v>
       </c>
       <c r="D8" t="n">
-        <v>35.9663271450819</v>
+        <v>36.04977569994287</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.09999939711293</v>
+        <v>6.878124415953151</v>
       </c>
       <c r="C9" t="n">
-        <v>47.7031209493525</v>
+        <v>42.26718391093791</v>
       </c>
       <c r="D9" t="n">
-        <v>34.05780960802609</v>
+        <v>33.9468721174462</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.267076433284139</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>31.60245859970483</v>
+        <v>30.89069151412589</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>29.31989518733098</v>
+        <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
-        <v>35.7169632282032</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -923,7 +923,7 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.12078032981814</v>
+        <v>27.55471281509523</v>
       </c>
       <c r="D12" t="n">
         <v>35.1485313074443</v>
@@ -937,7 +937,7 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.23582473766426</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
         <v>32.00006641992479</v>
@@ -951,7 +951,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>23.35381438862312</v>
       </c>
       <c r="D14" t="n">
         <v>30.72870314292517</v>
@@ -968,7 +968,7 @@
         <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -979,7 +979,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>18.59921025695582</v>
       </c>
       <c r="D16" t="n">
         <v>26.03889435973815</v>
@@ -993,7 +993,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
         <v>24.0832529328785</v>
@@ -1007,10 +1007,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.66547276580886</v>
+        <v>7.674197434128009</v>
       </c>
       <c r="C21" t="n">
-        <v>92.94385728543243</v>
+        <v>93.04964388880211</v>
       </c>
       <c r="D21" t="n">
-        <v>7.66547276580886</v>
+        <v>7.674197434128009</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.972953032637593</v>
+        <v>5.630323083855457</v>
       </c>
       <c r="C2" t="n">
-        <v>9.31973095641497</v>
+        <v>5.752059799182062</v>
       </c>
       <c r="D2" t="n">
-        <v>28.02889695624643</v>
+        <v>34.89033166122739</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.53401399784803</v>
+        <v>17.67636741496382</v>
       </c>
       <c r="C3" t="n">
-        <v>31.48464887519521</v>
+        <v>25.75615102091507</v>
       </c>
       <c r="D3" t="n">
-        <v>62.6207773153828</v>
+        <v>100.3198891584603</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.07271575003904</v>
+        <v>34.59973434077034</v>
       </c>
       <c r="C4" t="n">
-        <v>81.66864627317941</v>
+        <v>73.16867464981053</v>
       </c>
       <c r="D4" t="n">
-        <v>96.02670644778902</v>
+        <v>128.4184902017083</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.41779222031519</v>
+        <v>48.59651136021713</v>
       </c>
       <c r="C5" t="n">
-        <v>144.3659999094935</v>
+        <v>125.0746575210437</v>
       </c>
       <c r="D5" t="n">
-        <v>80.69966128908783</v>
+        <v>94.78774084502956</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44.75984133202059</v>
+        <v>47.49695393146069</v>
       </c>
       <c r="C6" t="n">
-        <v>176.906027566754</v>
+        <v>146.1940141348011</v>
       </c>
       <c r="D6" t="n">
-        <v>54.17872880656449</v>
+        <v>61.66553679915066</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>33.59638818703009</v>
+        <v>33.95570784678443</v>
       </c>
       <c r="C7" t="n">
-        <v>167.6226212753962</v>
+        <v>136.3618108767692</v>
       </c>
       <c r="D7" t="n">
-        <v>42.57937968088841</v>
+        <v>44.01665831990574</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>20.02765316663493</v>
+        <v>18.77592484372025</v>
       </c>
       <c r="C8" t="n">
-        <v>130.263194137988</v>
+        <v>107.2313929963579</v>
       </c>
       <c r="D8" t="n">
-        <v>37.63529824230147</v>
+        <v>38.46978379091126</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>9.540624189870499</v>
       </c>
       <c r="C9" t="n">
-        <v>77.10155595302322</v>
+        <v>64.23280704575605</v>
       </c>
       <c r="D9" t="n">
-        <v>35.49999698556465</v>
+        <v>35.16718451382499</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.121196935978863</v>
+        <v>5.978843518863076</v>
       </c>
       <c r="C10" t="n">
-        <v>43.13308538608361</v>
+        <v>39.71660337530471</v>
       </c>
       <c r="D10" t="n">
-        <v>35.3036474447153</v>
+        <v>35.58835427894688</v>
       </c>
     </row>
     <row r="11">
@@ -1217,7 +1217,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
         <v>32.69612554223576</v>
@@ -1237,7 +1237,7 @@
         <v>30.15830772675777</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>35.79943003535993</v>
       </c>
     </row>
     <row r="13">
@@ -1248,7 +1248,7 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>27.3171298706675</v>
+        <v>28.09761929554372</v>
       </c>
       <c r="D13" t="n">
         <v>32.780555844801</v>
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.57528845915541</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>29.74204670015712</v>
       </c>
     </row>
     <row r="16">
@@ -1290,7 +1290,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.25247339090745</v>
+        <v>19.83915760741954</v>
       </c>
       <c r="D16" t="n">
         <v>26.03889435973815</v>
@@ -1318,10 +1318,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.8391602716643</v>
+        <v>7.849467794515052</v>
       </c>
       <c r="C21" t="n">
-        <v>100.9291884976779</v>
+        <v>101.0618978543813</v>
       </c>
       <c r="D21" t="n">
-        <v>8.819055305622337</v>
+        <v>8.830651268829433</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.836891012374788</v>
+        <v>6.809402076655877</v>
       </c>
       <c r="C2" t="n">
-        <v>12.9129275539583</v>
+        <v>5.479133937401449</v>
       </c>
       <c r="D2" t="n">
-        <v>38.46487505239003</v>
+        <v>35.43912862790136</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.25068982194821</v>
+        <v>17.81872083207961</v>
       </c>
       <c r="C3" t="n">
-        <v>33.32542582065798</v>
+        <v>23.96937019918587</v>
       </c>
       <c r="D3" t="n">
-        <v>67.91239744127311</v>
+        <v>102.7938933731623</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.12376663065989</v>
+        <v>33.3489877655599</v>
       </c>
       <c r="C4" t="n">
-        <v>79.256492163845</v>
+        <v>68.31884099083128</v>
       </c>
       <c r="D4" t="n">
-        <v>102.7143718091183</v>
+        <v>142.3426178910408</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.86587008407924</v>
+        <v>49.57825906446394</v>
       </c>
       <c r="C5" t="n">
-        <v>146.599475936655</v>
+        <v>127.7253763225101</v>
       </c>
       <c r="D5" t="n">
-        <v>91.42525495798422</v>
+        <v>113.8091026148115</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>50.07305990740432</v>
+        <v>55.14476854754334</v>
       </c>
       <c r="C6" t="n">
-        <v>197.1928621273101</v>
+        <v>168.6544381125596</v>
       </c>
       <c r="D6" t="n">
-        <v>63.4366096576119</v>
+        <v>72.8554971321558</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>41.3816474817073</v>
+        <v>42.87881273068369</v>
       </c>
       <c r="C7" t="n">
-        <v>203.3749274209522</v>
+        <v>166.7243221260103</v>
       </c>
       <c r="D7" t="n">
-        <v>47.31042186765379</v>
+        <v>50.06520592577034</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>26.53664044579129</v>
+        <v>25.95250056176443</v>
       </c>
       <c r="C8" t="n">
-        <v>169.6509120323701</v>
+        <v>137.7735640754761</v>
       </c>
       <c r="D8" t="n">
-        <v>39.63806355896497</v>
+        <v>40.55599766243574</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14.08906130364597</v>
+        <v>13.31249886958674</v>
       </c>
       <c r="C9" t="n">
-        <v>111.0484280704694</v>
+        <v>93.2984295776871</v>
       </c>
       <c r="D9" t="n">
-        <v>36.94218436310322</v>
+        <v>36.83124687252333</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>7.260024272905163</v>
       </c>
       <c r="C10" t="n">
-        <v>62.35079669671494</v>
+        <v>54.23665192111504</v>
       </c>
       <c r="D10" t="n">
-        <v>35.73070769606267</v>
+        <v>35.87306111317846</v>
       </c>
     </row>
     <row r="11">
@@ -1531,7 +1531,7 @@
         <v>5.153193699591506</v>
       </c>
       <c r="C11" t="n">
-        <v>39.80397892098267</v>
+        <v>38.02701557629594</v>
       </c>
       <c r="D11" t="n">
         <v>36.78314123501524</v>
@@ -1545,10 +1545,10 @@
         <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>32.97886888105885</v>
+        <v>33.1958351236974</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>35.79943003535993</v>
       </c>
     </row>
     <row r="13">
@@ -1559,7 +1559,7 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>29.65859814529614</v>
+        <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
         <v>33.30088212805181</v>
@@ -1573,7 +1573,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>27.04125876577415</v>
+        <v>27.3485457972034</v>
       </c>
       <c r="D14" t="n">
         <v>30.72870314292517</v>
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>24.00864010735575</v>
+        <v>24.72531593145592</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>29.74204670015712</v>
       </c>
     </row>
     <row r="16">
@@ -1601,7 +1601,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.49242074137117</v>
+        <v>21.07910495788326</v>
       </c>
       <c r="D16" t="n">
         <v>26.03889435973815</v>
@@ -1615,7 +1615,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
         <v>24.0832529328785</v>
@@ -1632,7 +1632,7 @@
         <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.99639755568989</v>
+        <v>8.00890872682224</v>
       </c>
       <c r="C21" t="n">
-        <v>107.9513670018135</v>
+        <v>109.121381402953</v>
       </c>
       <c r="D21" t="n">
-        <v>9.995496944612363</v>
+        <v>10.0111359085278</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.31558298141973</v>
+        <v>6.243915399009714</v>
       </c>
       <c r="C2" t="n">
-        <v>8.986918484675302</v>
+        <v>3.768929436603505</v>
       </c>
       <c r="D2" t="n">
-        <v>31.42378051753191</v>
+        <v>29.33756664600743</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.87333885061894</v>
+        <v>22.15804568485051</v>
       </c>
       <c r="C3" t="n">
-        <v>51.58102438112742</v>
+        <v>36.92353115672254</v>
       </c>
       <c r="D3" t="n">
-        <v>74.06795554690062</v>
+        <v>110.5644264522758</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.55623434214721</v>
+        <v>23.81523580961913</v>
       </c>
       <c r="C4" t="n">
-        <v>115.7833972480518</v>
+        <v>101.1445572300276</v>
       </c>
       <c r="D4" t="n">
-        <v>99.90657337497241</v>
+        <v>133.8171208273615</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.20070280448963</v>
+        <v>31.04777114680538</v>
       </c>
       <c r="C5" t="n">
-        <v>117.8342682022234</v>
+        <v>100.7764018409351</v>
       </c>
       <c r="D5" t="n">
-        <v>62.46369768270332</v>
+        <v>74.12195167063419</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>25.68055644768807</v>
+        <v>26.60634453279281</v>
       </c>
       <c r="C6" t="n">
-        <v>133.9575107490688</v>
+        <v>109.8065172245973</v>
       </c>
       <c r="D6" t="n">
-        <v>31.15478164656829</v>
+        <v>32.96610616090365</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.54677671800324</v>
+        <v>17.18745705824891</v>
       </c>
       <c r="C7" t="n">
-        <v>119.2941270384384</v>
+        <v>96.83664830379264</v>
       </c>
       <c r="D7" t="n">
-        <v>27.84727363096077</v>
+        <v>28.50602634051038</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.763480918734528</v>
+        <v>9.179341034707678</v>
       </c>
       <c r="C8" t="n">
-        <v>81.77958376375931</v>
+        <v>68.76160920544659</v>
       </c>
       <c r="D8" t="n">
-        <v>27.20422888467911</v>
+        <v>27.12078032981814</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.324999547834698</v>
+        <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>47.59218345877262</v>
+        <v>41.3796839862988</v>
       </c>
       <c r="D9" t="n">
-        <v>27.17968519207294</v>
+        <v>27.29062268265283</v>
       </c>
     </row>
     <row r="10">
@@ -1828,7 +1828,7 @@
         <v>3.701188845010476</v>
       </c>
       <c r="C10" t="n">
-        <v>31.17539834835747</v>
+        <v>29.75186417719959</v>
       </c>
       <c r="D10" t="n">
         <v>28.75539025738908</v>
@@ -1842,10 +1842,10 @@
         <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>26.29905750136355</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>28.43141351498762</v>
+        <v>28.60910984945629</v>
       </c>
     </row>
     <row r="12">
@@ -1856,7 +1856,7 @@
         <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>24.0832529328785</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
         <v>27.12078032981814</v>
@@ -1870,7 +1870,7 @@
         <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>22.37403017978481</v>
+        <v>22.63419332141022</v>
       </c>
       <c r="D13" t="n">
         <v>25.49598787928967</v>
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>19.97365704290136</v>
+        <v>20.58823110575986</v>
       </c>
       <c r="D14" t="n">
-        <v>24.58296251434014</v>
+        <v>24.89024954576939</v>
       </c>
     </row>
     <row r="15">
@@ -1898,7 +1898,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
         <v>21.85861263505523</v>
@@ -1912,7 +1912,7 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>16.11931555602838</v>
       </c>
       <c r="D16" t="n">
         <v>20.25247339090745</v>
@@ -1929,7 +1929,7 @@
         <v>15.58328130950962</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>17.47216389248049</v>
       </c>
     </row>
     <row r="18">
@@ -1968,7 +1968,7 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>72.62969516017901</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
         <v>6.724971774090649</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.800345363139403</v>
+        <v>3.86612245932394</v>
       </c>
       <c r="C2" t="n">
-        <v>3.976078202199582</v>
+        <v>2.144136986075034</v>
       </c>
       <c r="D2" t="n">
-        <v>21.35890305359361</v>
+        <v>21.237166338267</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.33476027161494</v>
+        <v>22.44766125760332</v>
       </c>
       <c r="C3" t="n">
-        <v>44.21791659927634</v>
+        <v>26.11939767148639</v>
       </c>
       <c r="D3" t="n">
-        <v>81.80412745636548</v>
+        <v>110.1668186320558</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.94134148411922</v>
+        <v>32.09824119034946</v>
       </c>
       <c r="C4" t="n">
-        <v>124.972555759802</v>
+        <v>100.5447093827328</v>
       </c>
       <c r="D4" t="n">
-        <v>111.1632925518663</v>
+        <v>153.1526418625024</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.39138284329177</v>
+        <v>34.31208226342603</v>
       </c>
       <c r="C5" t="n">
-        <v>163.2891869088508</v>
+        <v>141.2980383337222</v>
       </c>
       <c r="D5" t="n">
-        <v>78.53981633974485</v>
+        <v>96.13764393836894</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.14849024971531</v>
+        <v>31.95981476405067</v>
       </c>
       <c r="C6" t="n">
-        <v>162.053166549204</v>
+        <v>134.0782657166912</v>
       </c>
       <c r="D6" t="n">
-        <v>37.83655652167208</v>
+        <v>42.02272873258048</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.5287043486993</v>
+        <v>15.9897248590678</v>
       </c>
       <c r="C7" t="n">
-        <v>148.9379989681709</v>
+        <v>122.8873236359817</v>
       </c>
       <c r="D7" t="n">
-        <v>30.30262463928205</v>
+        <v>31.56024344842221</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.17795837637593</v>
+        <v>7.844164156932015</v>
       </c>
       <c r="C8" t="n">
-        <v>107.7320843255237</v>
+        <v>88.95615948180348</v>
       </c>
       <c r="D8" t="n">
-        <v>27.95526587842792</v>
+        <v>27.87181732356695</v>
       </c>
     </row>
     <row r="9">
@@ -2125,10 +2125,10 @@
         <v>4.437499623195581</v>
       </c>
       <c r="C9" t="n">
-        <v>51.47499562906875</v>
+        <v>46.48280855297372</v>
       </c>
       <c r="D9" t="n">
-        <v>28.39999758845172</v>
+        <v>28.28906009787183</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>33.16834618797849</v>
+        <v>32.31422568528377</v>
       </c>
       <c r="D10" t="n">
-        <v>29.60951076008381</v>
+        <v>30.03657101143117</v>
       </c>
     </row>
     <row r="11">
@@ -2153,10 +2153,10 @@
         <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>28.78680618392497</v>
+        <v>29.31989518733098</v>
       </c>
       <c r="D11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.67528785626833</v>
       </c>
     </row>
     <row r="12">
@@ -2167,7 +2167,7 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>20.39482680802324</v>
+        <v>20.61179305066178</v>
       </c>
       <c r="D12" t="n">
         <v>28.42257778564941</v>
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.3902779224005</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>26.01631416254048</v>
       </c>
     </row>
     <row r="14">
@@ -2195,7 +2195,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>14.74977750860408</v>
       </c>
       <c r="D14" t="n">
         <v>18.12993485432585</v>
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="D15" t="n">
         <v>17.20021977840412</v>
@@ -2226,7 +2226,7 @@
         <v>13.22610507161303</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2265,7 +2265,7 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>63.19019098384595</v>
+        <v>63.79200232654924</v>
       </c>
       <c r="D19" t="n">
         <v>5.416302084329653</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.691371367968007</v>
+        <v>4.336379609658161</v>
       </c>
       <c r="C2" t="n">
-        <v>4.332452618841174</v>
+        <v>8.003207285019998</v>
       </c>
       <c r="D2" t="n">
-        <v>23.50304003966864</v>
+        <v>21.29705294822606</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.64691498383642</v>
+        <v>17.7745421853885</v>
       </c>
       <c r="C3" t="n">
-        <v>29.17263303169397</v>
+        <v>16.66025854106837</v>
       </c>
       <c r="D3" t="n">
-        <v>79.7031873692773</v>
+        <v>102.2195709661779</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.5952265128766</v>
+        <v>37.33095645398497</v>
       </c>
       <c r="C4" t="n">
-        <v>117.570178069781</v>
+        <v>83.4299016545982</v>
       </c>
       <c r="D4" t="n">
-        <v>124.3471824721968</v>
+        <v>170.2419241503267</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.47821860962199</v>
+        <v>40.57072387799944</v>
       </c>
       <c r="C5" t="n">
-        <v>196.9385894719102</v>
+        <v>162.3319828972101</v>
       </c>
       <c r="D5" t="n">
-        <v>96.92304210176638</v>
+        <v>123.675667042492</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.86422538384024</v>
+        <v>38.23907308041327</v>
       </c>
       <c r="C6" t="n">
-        <v>206.2092330431128</v>
+        <v>177.1877891578729</v>
       </c>
       <c r="D6" t="n">
-        <v>50.4353248102714</v>
+        <v>58.08313942635406</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.83487076370406</v>
+        <v>24.67328330313084</v>
       </c>
       <c r="C7" t="n">
-        <v>189.121914250697</v>
+        <v>155.1063197939536</v>
       </c>
       <c r="D7" t="n">
-        <v>33.53650157707104</v>
+        <v>35.45287309576081</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.76624623539802</v>
+        <v>11.26555490623215</v>
       </c>
       <c r="C8" t="n">
-        <v>147.7873906587936</v>
+        <v>122.8362727553609</v>
       </c>
       <c r="D8" t="n">
-        <v>29.45733986592554</v>
+        <v>29.6242369756475</v>
       </c>
     </row>
     <row r="9">
@@ -2436,10 +2436,10 @@
         <v>5.546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>85.19999276535516</v>
+        <v>73.99530621678632</v>
       </c>
       <c r="D9" t="n">
-        <v>29.39843500367073</v>
+        <v>29.28749751309084</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.704714925199962</v>
+        <v>2.562361508084175</v>
       </c>
       <c r="C10" t="n">
-        <v>44.69897297435728</v>
+        <v>41.70955121492574</v>
       </c>
       <c r="D10" t="n">
-        <v>29.89421759431538</v>
+        <v>30.32127784566274</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>32.87382187670443</v>
+        <v>33.22921454564179</v>
       </c>
       <c r="D11" t="n">
-        <v>30.03068052520567</v>
+        <v>30.20837685967435</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>25.16808414607123</v>
       </c>
       <c r="D12" t="n">
-        <v>29.07347651356504</v>
+        <v>28.8565102709265</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.47158305540374</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>26.79680358741669</v>
       </c>
     </row>
     <row r="14">
@@ -2506,7 +2506,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>15.97892563432109</v>
       </c>
       <c r="D14" t="n">
         <v>18.74450891718435</v>
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.40853021815369</v>
+        <v>15.0501923061036</v>
       </c>
       <c r="D15" t="n">
-        <v>16.84188186635403</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2537,7 +2537,7 @@
         <v>14.46605242207675</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -2548,7 +2548,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.16661937228147</v>
+        <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
         <v>10.86107485208246</v>
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>33.7014351913845</v>
+        <v>34.3032465340878</v>
       </c>
       <c r="D19" t="n">
         <v>3.610868056219768</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.244275251908209</v>
+        <v>2.59475918232432</v>
       </c>
       <c r="C2" t="n">
-        <v>2.138246499849553</v>
+        <v>3.732604771546373</v>
       </c>
       <c r="D2" t="n">
-        <v>16.40304064255571</v>
+        <v>14.86366024229671</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.21494599396782</v>
+        <v>18.02979658849267</v>
       </c>
       <c r="C3" t="n">
-        <v>25.69233742013903</v>
+        <v>23.99882263031328</v>
       </c>
       <c r="D3" t="n">
-        <v>81.84830610305659</v>
+        <v>100.3689765436727</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.97734735400687</v>
+        <v>41.00661985868502</v>
       </c>
       <c r="C4" t="n">
-        <v>114.3156844302029</v>
+        <v>77.40589774133977</v>
       </c>
       <c r="D4" t="n">
-        <v>134.1744769917073</v>
+        <v>182.0984911745154</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.50905369908114</v>
+        <v>41.67519004527711</v>
       </c>
       <c r="C5" t="n">
-        <v>233.5332351477101</v>
+        <v>186.7284133477434</v>
       </c>
       <c r="D5" t="n">
-        <v>102.2981107825177</v>
+        <v>130.7687942056752</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.02144388523996</v>
+        <v>30.83276839957533</v>
       </c>
       <c r="C6" t="n">
-        <v>242.6772332650649</v>
+        <v>209.7111271041612</v>
       </c>
       <c r="D6" t="n">
-        <v>49.50953672516665</v>
+        <v>56.47307319138928</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.785259294677205</v>
+        <v>7.425939634922873</v>
       </c>
       <c r="C7" t="n">
-        <v>195.0506886366435</v>
+        <v>161.3944138396544</v>
       </c>
       <c r="D7" t="n">
-        <v>33.71616140694821</v>
+        <v>35.2133266559246</v>
       </c>
     </row>
     <row r="8">
@@ -2733,7 +2733,7 @@
         <v>3.838633523605028</v>
       </c>
       <c r="C8" t="n">
-        <v>106.2300103380261</v>
+        <v>91.79341034707677</v>
       </c>
       <c r="D8" t="n">
         <v>31.29320807286708</v>
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>34.05780960802609</v>
+        <v>31.8390597964283</v>
       </c>
       <c r="D9" t="n">
-        <v>31.39530983410874</v>
+        <v>31.72812230584841</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>25.76596849795754</v>
+        <v>26.05067533218912</v>
       </c>
       <c r="D10" t="n">
-        <v>23.48831382410494</v>
+        <v>23.63066724122073</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>19.72429312602266</v>
+        <v>20.07968579496001</v>
       </c>
       <c r="D11" t="n">
-        <v>23.27821981539612</v>
+        <v>23.10052348092744</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>14.97067074205961</v>
+        <v>15.4046032273367</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>21.69662426385451</v>
       </c>
     </row>
     <row r="13">
@@ -2803,7 +2803,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>13.00815708127024</v>
       </c>
       <c r="D13" t="n">
         <v>15.34962535589888</v>
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.90605532002857</v>
+        <v>12.59876828859932</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -2834,7 +2834,7 @@
         <v>12.18348900970292</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>12.18348900970292</v>
       </c>
     </row>
     <row r="16">
@@ -2845,7 +2845,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>11.98615772114931</v>
+        <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
         <v>9.092947236733956</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>28.89283493598363</v>
+        <v>29.42788743479814</v>
       </c>
       <c r="D18" t="n">
         <v>2.675262494072558</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.729258617806133</v>
+        <v>3.100359250011427</v>
       </c>
       <c r="C2" t="n">
-        <v>4.085052197370977</v>
+        <v>7.37488875430204</v>
       </c>
       <c r="D2" t="n">
-        <v>15.33686263574367</v>
+        <v>13.41656412623691</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.68418033886879</v>
+        <v>13.62174939642449</v>
       </c>
       <c r="C3" t="n">
-        <v>17.01368771459722</v>
+        <v>19.21280257211008</v>
       </c>
       <c r="D3" t="n">
-        <v>76.49778111491146</v>
+        <v>91.04237335332796</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.39927788265474</v>
+        <v>38.27539774547039</v>
       </c>
       <c r="C4" t="n">
-        <v>91.13858462834415</v>
+        <v>69.46748580480005</v>
       </c>
       <c r="D4" t="n">
-        <v>142.1639398088679</v>
+        <v>188.6712920544478</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.60847225911733</v>
+        <v>50.06913291658734</v>
       </c>
       <c r="C5" t="n">
-        <v>224.9920301207628</v>
+        <v>167.9034011188108</v>
       </c>
       <c r="D5" t="n">
-        <v>121.5894531709675</v>
+        <v>158.3804483876167</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.31328499530853</v>
+        <v>40.37241084174159</v>
       </c>
       <c r="C6" t="n">
-        <v>299.4723197034471</v>
+        <v>249.7212730430358</v>
       </c>
       <c r="D6" t="n">
-        <v>65.20768251607315</v>
+        <v>76.96116603131597</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.10949807898591</v>
+        <v>16.82813739849458</v>
       </c>
       <c r="C7" t="n">
-        <v>260.3270934920139</v>
+        <v>221.9397765082594</v>
       </c>
       <c r="D7" t="n">
-        <v>38.0279973240002</v>
+        <v>41.3816474817073</v>
       </c>
     </row>
     <row r="8">
@@ -3044,10 +3044,10 @@
         <v>5.006913291658733</v>
       </c>
       <c r="C8" t="n">
-        <v>167.6481467157066</v>
+        <v>142.6970288122739</v>
       </c>
       <c r="D8" t="n">
-        <v>32.96217917008666</v>
+        <v>33.12907627980861</v>
       </c>
     </row>
     <row r="9">
@@ -3058,10 +3058,10 @@
         <v>2.218749811597791</v>
       </c>
       <c r="C9" t="n">
-        <v>67.22811929141305</v>
+        <v>60.68280734719958</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>32.50468473990763</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>31.46010518258904</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D10" t="n">
-        <v>24.76949457814703</v>
+        <v>24.91184799526281</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>23.10052348092744</v>
+        <v>23.63361248433346</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>23.81130881880213</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.14033316844506</v>
+        <v>17.57426565372215</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>21.91359050649305</v>
       </c>
     </row>
     <row r="13">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.82791641431633</v>
+        <v>13.52062938288707</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -3145,7 +3145,7 @@
         <v>13.25850274585317</v>
       </c>
       <c r="D15" t="n">
-        <v>11.82515109765283</v>
+        <v>11.46681318560274</v>
       </c>
     </row>
     <row r="16">
@@ -3156,7 +3156,7 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.1456838753228</v>
+        <v>23.55899965881071</v>
       </c>
       <c r="D16" t="n">
         <v>8.266315669758143</v>
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.0554452019901</v>
+        <v>33.52766584773283</v>
       </c>
       <c r="D17" t="n">
         <v>4.249985811684442</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.848630927096744</v>
+        <v>2.069524160552276</v>
       </c>
       <c r="C2" t="n">
-        <v>2.363066724122073</v>
+        <v>4.225442119078272</v>
       </c>
       <c r="D2" t="n">
-        <v>12.34056864238241</v>
+        <v>9.919578803709772</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.38336463074177</v>
+        <v>12.46328710541326</v>
       </c>
       <c r="C3" t="n">
-        <v>16.66025854106837</v>
+        <v>23.67484588791183</v>
       </c>
       <c r="D3" t="n">
-        <v>72.47752426602078</v>
+        <v>83.21293541195965</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.64703815702343</v>
+        <v>34.48486985937346</v>
       </c>
       <c r="C4" t="n">
-        <v>73.39840361260428</v>
+        <v>62.15444715586556</v>
       </c>
       <c r="D4" t="n">
-        <v>146.2862984190002</v>
+        <v>193.0106169072187</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.41274461307373</v>
+        <v>54.04521111878692</v>
       </c>
       <c r="C5" t="n">
-        <v>211.762979806037</v>
+        <v>157.0550889868835</v>
       </c>
       <c r="D5" t="n">
-        <v>136.2420376568511</v>
+        <v>176.6654993792135</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>43.83405324691584</v>
+        <v>47.97997380195012</v>
       </c>
       <c r="C6" t="n">
-        <v>332.2371675849801</v>
+        <v>270.5716307858295</v>
       </c>
       <c r="D6" t="n">
-        <v>75.99512629033711</v>
+        <v>94.06811977781665</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>14.43267300013236</v>
+        <v>15.15131231964102</v>
       </c>
       <c r="C7" t="n">
-        <v>317.2792595630757</v>
+        <v>270.0287243053809</v>
       </c>
       <c r="D7" t="n">
-        <v>42.33983324105218</v>
+        <v>46.41212271826796</v>
       </c>
     </row>
     <row r="8">
@@ -3355,7 +3355,7 @@
         <v>4.088979188187965</v>
       </c>
       <c r="C8" t="n">
-        <v>215.6310657607694</v>
+        <v>184.9219975719292</v>
       </c>
       <c r="D8" t="n">
         <v>34.21390749300134</v>
@@ -3369,10 +3369,10 @@
         <v>1.664062358698343</v>
       </c>
       <c r="C9" t="n">
-        <v>73.99530621678632</v>
+        <v>69.11405663127118</v>
       </c>
       <c r="D9" t="n">
-        <v>31.8390597964283</v>
+        <v>32.39374724932775</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>31.8871654339364</v>
+        <v>31.74481201682062</v>
       </c>
       <c r="D10" t="n">
-        <v>25.48126166372597</v>
+        <v>25.33890824661018</v>
       </c>
     </row>
     <row r="11">
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.7451308119901</v>
+        <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
         <v>24.16670148773948</v>
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.48943444052943</v>
+        <v>16.70640068316797</v>
       </c>
       <c r="D12" t="n">
-        <v>19.30999559483051</v>
+        <v>19.96089432274615</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.44717823151781</v>
+        <v>11.18701508989241</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -3442,7 +3442,7 @@
         <v>11.06233313145306</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>10.75504610002381</v>
       </c>
     </row>
     <row r="15">
@@ -3453,7 +3453,7 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
         <v>6.808420328951629</v>
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.10547327717769</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
         <v>3.306526267903257</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.520146356801562</v>
+        <v>3.353650157707104</v>
       </c>
       <c r="C2" t="n">
-        <v>8.583420178229863</v>
+        <v>12.49961177047039</v>
       </c>
       <c r="D2" t="n">
-        <v>14.44347222487907</v>
+        <v>15.21905291123405</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>8.963356539773379</v>
+        <v>9.856746950637977</v>
       </c>
       <c r="C3" t="n">
-        <v>13.17996292951343</v>
+        <v>20.16018910670825</v>
       </c>
       <c r="D3" t="n">
-        <v>67.23990026386404</v>
+        <v>73.85197105196632</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.73339089726815</v>
+        <v>29.62227348023901</v>
       </c>
       <c r="C4" t="n">
-        <v>59.44875048296136</v>
+        <v>60.59739529693012</v>
       </c>
       <c r="D4" t="n">
-        <v>146.0948576166721</v>
+        <v>190.4963610366426</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.70097752749479</v>
+        <v>53.08800710714628</v>
       </c>
       <c r="C5" t="n">
-        <v>179.5616551067417</v>
+        <v>138.6473195322558</v>
       </c>
       <c r="D5" t="n">
-        <v>151.5818455357075</v>
+        <v>197.4294633240336</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>52.44790760397736</v>
+        <v>57.27810630887167</v>
       </c>
       <c r="C6" t="n">
-        <v>335.1352868079167</v>
+        <v>263.2860810726139</v>
       </c>
       <c r="D6" t="n">
-        <v>93.38384162795661</v>
+        <v>117.2530735613093</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.35010838198439</v>
+        <v>28.92523261022377</v>
       </c>
       <c r="C7" t="n">
-        <v>384.4121493271768</v>
+        <v>319.2555176917245</v>
       </c>
       <c r="D7" t="n">
-        <v>50.18497914568845</v>
+        <v>56.89227946110266</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.42692138262712</v>
+        <v>7.844164156932015</v>
       </c>
       <c r="C8" t="n">
-        <v>290.9851108002334</v>
+        <v>254.1008495516807</v>
       </c>
       <c r="D8" t="n">
-        <v>36.46701847424777</v>
+        <v>37.1346069131356</v>
       </c>
     </row>
     <row r="9">
@@ -3680,10 +3680,10 @@
         <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>141.3343629987793</v>
+        <v>126.9124892233936</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>33.28124717396686</v>
       </c>
     </row>
     <row r="10">
@@ -3694,7 +3694,7 @@
         <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>50.1084028247572</v>
+        <v>48.68486865359933</v>
       </c>
       <c r="D10" t="n">
         <v>26.47773558353648</v>
@@ -3708,7 +3708,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.18753917370691</v>
+        <v>27.72062817711293</v>
       </c>
       <c r="D11" t="n">
         <v>24.6997904911455</v>
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.30999559483051</v>
+        <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
-        <v>19.7439280801076</v>
+        <v>20.39482680802324</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>13.00815708127024</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
         <v>2.89321048441535</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.993168823799278</v>
+        <v>4.220533380557038</v>
       </c>
       <c r="C2" t="n">
-        <v>9.588729827378597</v>
+        <v>7.994371555681777</v>
       </c>
       <c r="D2" t="n">
-        <v>11.8516582856675</v>
+        <v>10.35743827980385</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.82212373908208</v>
+        <v>2.397427893770711</v>
       </c>
       <c r="C2" t="n">
-        <v>5.011822030179967</v>
+        <v>7.200137662946108</v>
       </c>
       <c r="D2" t="n">
-        <v>10.74522862298134</v>
+        <v>11.20075955775186</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.18839774822415</v>
+        <v>13.55793579564845</v>
       </c>
       <c r="C3" t="n">
-        <v>20.78359889890498</v>
+        <v>31.41592653589793</v>
       </c>
       <c r="D3" t="n">
-        <v>72.36953201855363</v>
+        <v>80.68984381204535</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.81593981988289</v>
+        <v>40.63650097418398</v>
       </c>
       <c r="C4" t="n">
-        <v>90.50044862058371</v>
+        <v>86.03349656626072</v>
       </c>
       <c r="D4" t="n">
-        <v>149.3493512562503</v>
+        <v>194.7080586878614</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.4587225242573</v>
+        <v>33.23215978875454</v>
       </c>
       <c r="C5" t="n">
-        <v>275.9692796637784</v>
+        <v>215.0272909226577</v>
       </c>
       <c r="D5" t="n">
-        <v>137.5919407501905</v>
+        <v>177.1809169239431</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>16.34217228489241</v>
+        <v>17.95223851985718</v>
       </c>
       <c r="C6" t="n">
-        <v>315.5729820530948</v>
+        <v>261.8772731170197</v>
       </c>
       <c r="D6" t="n">
-        <v>73.58002693788995</v>
+        <v>90.04295419040471</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4.910702016642545</v>
+        <v>5.150248456478767</v>
       </c>
       <c r="C7" t="n">
-        <v>204.6325462300924</v>
+        <v>178.7016441178214</v>
       </c>
       <c r="D7" t="n">
-        <v>32.03933632809466</v>
+        <v>33.35684174719388</v>
       </c>
     </row>
     <row r="8">
@@ -4288,10 +4288,10 @@
         <v>1.585522542358599</v>
       </c>
       <c r="C8" t="n">
-        <v>104.1437964665016</v>
+        <v>93.54582999915733</v>
       </c>
       <c r="D8" t="n">
-        <v>24.20008090968387</v>
+        <v>24.53387512912779</v>
       </c>
     </row>
     <row r="9">
@@ -4302,7 +4302,7 @@
         <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>38.162496759482</v>
+        <v>37.16405934426299</v>
       </c>
       <c r="D9" t="n">
         <v>20.1906232855399</v>
@@ -4316,7 +4316,7 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>21.21065915025234</v>
+        <v>21.6377194015997</v>
       </c>
       <c r="D10" t="n">
         <v>19.3600647277471</v>
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.45958109877452</v>
+        <v>15.81497376771187</v>
       </c>
       <c r="D11" t="n">
-        <v>15.81497376771187</v>
+        <v>16.34806277111788</v>
       </c>
     </row>
     <row r="12">
@@ -4347,7 +4347,7 @@
         <v>10.63134588928871</v>
       </c>
       <c r="D12" t="n">
-        <v>13.0179745583127</v>
+        <v>13.23494080095125</v>
       </c>
     </row>
     <row r="13">
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.57528845915541</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
         <v>2.150027472300515</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.31558298141973</v>
+        <v>5.820782138479339</v>
       </c>
       <c r="C2" t="n">
-        <v>8.344855486097888</v>
+        <v>5.253331965424683</v>
       </c>
       <c r="D2" t="n">
-        <v>12.54869915568273</v>
+        <v>24.03514729537041</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.61269268290802</v>
+        <v>8.973174016815847</v>
       </c>
       <c r="C3" t="n">
-        <v>24.16081100151401</v>
+        <v>20.14546289114455</v>
       </c>
       <c r="D3" t="n">
-        <v>13.09160563613122</v>
+        <v>11.8349685746953</v>
       </c>
     </row>
     <row r="4">
@@ -4554,7 +4554,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>4.68784528777852</v>
       </c>
       <c r="C5" t="n">
         <v>9.35114688295087</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>8.130834486572086</v>
       </c>
       <c r="C6" t="n">
         <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>32.52333794628834</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>32.69808903764427</v>
       </c>
     </row>
     <row r="8">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39746438408754</v>
+        <v>13.39812685213415</v>
       </c>
       <c r="C21" t="n">
-        <v>70.13966648139949</v>
+        <v>70.14313469646703</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576172280480887</v>
+        <v>1.576250217898135</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.62599518241097</v>
+        <v>4.483641765295182</v>
       </c>
       <c r="C2" t="n">
-        <v>6.49131582047991</v>
+        <v>5.361324212891832</v>
       </c>
       <c r="D2" t="n">
-        <v>18.11815388187489</v>
+        <v>25.19360958638165</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.3131207643925</v>
+        <v>15.61960597456675</v>
       </c>
       <c r="C3" t="n">
-        <v>29.40334374219197</v>
+        <v>20.35653864755761</v>
       </c>
       <c r="D3" t="n">
-        <v>20.469439633546</v>
+        <v>29.1628155546515</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>12.4181267110179</v>
+        <v>10.56753228851267</v>
       </c>
       <c r="C4" t="n">
-        <v>37.36924461445059</v>
+        <v>31.2559016601057</v>
       </c>
       <c r="D4" t="n">
-        <v>21.92635322664826</v>
+        <v>21.27545449873262</v>
       </c>
     </row>
     <row r="5">
@@ -4865,7 +4865,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>3.043417883165113</v>
       </c>
       <c r="C5" t="n">
         <v>5.375068680751288</v>
@@ -4885,7 +4885,7 @@
         <v>16.50317890838889</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>34.3346624606237</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.521970983489814</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>35.27321326588365</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>36.80081269369168</v>
       </c>
     </row>
     <row r="9">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43934726235935</v>
+        <v>15.43988209032375</v>
       </c>
       <c r="C21" t="n">
-        <v>86.13530577947849</v>
+        <v>86.13828955654303</v>
       </c>
       <c r="D21" t="n">
-        <v>3.25038889733881</v>
+        <v>3.250501492699737</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.956443248114646</v>
+        <v>4.837070938824034</v>
       </c>
       <c r="C2" t="n">
-        <v>5.504659377711866</v>
+        <v>7.966882619962866</v>
       </c>
       <c r="D2" t="n">
-        <v>30.00810032800801</v>
+        <v>21.5601613329642</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.58662746324986</v>
+        <v>15.57051858935441</v>
       </c>
       <c r="C3" t="n">
-        <v>26.89006961932013</v>
+        <v>20.66088043587412</v>
       </c>
       <c r="D3" t="n">
-        <v>30.21328559819559</v>
+        <v>42.54894550205677</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.38955821660351</v>
+        <v>21.72214970416493</v>
       </c>
       <c r="C4" t="n">
-        <v>58.72127543411447</v>
+        <v>42.86997700134547</v>
       </c>
       <c r="D4" t="n">
-        <v>27.26117025152543</v>
+        <v>31.08998629808799</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>11.06920536538279</v>
+        <v>9.645671194224914</v>
       </c>
       <c r="C5" t="n">
-        <v>41.62610266006477</v>
+        <v>35.19565519724816</v>
       </c>
       <c r="D5" t="n">
-        <v>30.53235360207581</v>
+        <v>30.31146036862028</v>
       </c>
     </row>
     <row r="6">
@@ -5196,7 +5196,7 @@
         <v>12.23650338573225</v>
       </c>
       <c r="D6" t="n">
-        <v>36.54850353370026</v>
+        <v>36.34724525432967</v>
       </c>
     </row>
     <row r="7">
@@ -5210,7 +5210,7 @@
         <v>24.25407703341745</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>37.66867766424586</v>
       </c>
     </row>
     <row r="8">
@@ -5224,7 +5224,7 @@
         <v>29.87458264023044</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>38.05254101660637</v>
       </c>
     </row>
     <row r="9">
@@ -5238,7 +5238,7 @@
         <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>41.26874649571891</v>
       </c>
     </row>
     <row r="10">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73027254007201</v>
+        <v>16.73175065010522</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0546624944393</v>
+        <v>102.0636789656418</v>
       </c>
       <c r="D21" t="n">
-        <v>4.182568135018002</v>
+        <v>4.182937662526304</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.274930414918113</v>
+        <v>6.465790380169493</v>
       </c>
       <c r="C2" t="n">
-        <v>11.88896469842888</v>
+        <v>4.885176576332128</v>
       </c>
       <c r="D2" t="n">
-        <v>27.13648829308609</v>
+        <v>27.84040139703105</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.90783888898781</v>
+        <v>16.12029730373262</v>
       </c>
       <c r="C3" t="n">
-        <v>23.94482650657971</v>
+        <v>26.57100161543993</v>
       </c>
       <c r="D3" t="n">
-        <v>46.29922173227958</v>
+        <v>49.47026681699678</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.32047602440774</v>
+        <v>26.38054256081604</v>
       </c>
       <c r="C4" t="n">
-        <v>62.84363404424683</v>
+        <v>47.80914970141117</v>
       </c>
       <c r="D4" t="n">
-        <v>35.78666731520473</v>
+        <v>44.64399510291945</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>23.80738182798515</v>
+        <v>20.98485717827558</v>
       </c>
       <c r="C5" t="n">
-        <v>77.70533079113505</v>
+        <v>58.61033794353459</v>
       </c>
       <c r="D5" t="n">
-        <v>33.08489763311751</v>
+        <v>34.18936380039518</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.38492721552276</v>
+        <v>9.620145753914496</v>
       </c>
       <c r="C6" t="n">
-        <v>39.92964262712628</v>
+        <v>35.22019888985433</v>
       </c>
       <c r="D6" t="n">
-        <v>38.35982804803563</v>
+        <v>38.11831811279092</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>8.563785224144926</v>
       </c>
       <c r="C7" t="n">
         <v>21.19985992550562</v>
       </c>
       <c r="D7" t="n">
-        <v>39.52516257297658</v>
+        <v>39.64493579289469</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.6814150222053</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="C8" t="n">
-        <v>31.71045084717197</v>
+        <v>31.37665662772806</v>
       </c>
       <c r="D8" t="n">
-        <v>39.8884092235479</v>
+        <v>40.05530633326986</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>10.6499990956694</v>
       </c>
       <c r="C9" t="n">
-        <v>33.9468721174462</v>
+        <v>34.39062207976576</v>
       </c>
       <c r="D9" t="n">
-        <v>42.15624642035802</v>
+        <v>41.82343394861835</v>
       </c>
     </row>
     <row r="10">
@@ -5563,7 +5563,7 @@
         <v>33.59540643932586</v>
       </c>
       <c r="D10" t="n">
-        <v>48.68486865359933</v>
+        <v>49.25428232206248</v>
       </c>
     </row>
     <row r="11">
@@ -5574,7 +5574,7 @@
         <v>8.707120388964958</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>33.22921454564179</v>
       </c>
       <c r="D11" t="n">
         <v>50.82115165804038</v>
@@ -5588,7 +5588,7 @@
         <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
-        <v>33.84673385161303</v>
+        <v>34.28066633689012</v>
       </c>
       <c r="D12" t="n">
         <v>47.08167465256428</v>
@@ -5616,10 +5616,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.42141611149592</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>43.71722527011046</v>
       </c>
     </row>
     <row r="16">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.05005835776237</v>
+        <v>18.05617543183745</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7551426196878</v>
+        <v>117.7950492457967</v>
       </c>
       <c r="D21" t="n">
-        <v>6.016686119254122</v>
+        <v>6.018725143945816</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.865942532874692</v>
+        <v>6.776022654711485</v>
       </c>
       <c r="C2" t="n">
-        <v>9.767407909551517</v>
+        <v>11.76035574917254</v>
       </c>
       <c r="D2" t="n">
-        <v>23.98802340556657</v>
+        <v>38.73780091417064</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.95692627420016</v>
+        <v>17.37693436516854</v>
       </c>
       <c r="C3" t="n">
-        <v>34.20899875448011</v>
+        <v>20.86704745376596</v>
       </c>
       <c r="D3" t="n">
-        <v>53.26963043243193</v>
+        <v>56.09706382066275</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>20.58626761035137</v>
+        <v>21.04572553593887</v>
       </c>
       <c r="C4" t="n">
-        <v>50.66799901617789</v>
+        <v>48.76635371305181</v>
       </c>
       <c r="D4" t="n">
-        <v>43.75060469205486</v>
+        <v>51.12745694176539</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>20.19945901487813</v>
+        <v>18.70229376590174</v>
       </c>
       <c r="C5" t="n">
-        <v>73.0420291959627</v>
+        <v>54.97787143782139</v>
       </c>
       <c r="D5" t="n">
-        <v>30.72870314292517</v>
+        <v>33.79666471869646</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.63272854762046</v>
+        <v>10.34467555964864</v>
       </c>
       <c r="C6" t="n">
-        <v>55.70829172978102</v>
+        <v>44.39757642915352</v>
       </c>
       <c r="D6" t="n">
-        <v>31.23528495831652</v>
+        <v>31.31578827006476</v>
       </c>
     </row>
     <row r="7">
@@ -5826,10 +5826,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.270021676396877</v>
+        <v>5.090361846519712</v>
       </c>
       <c r="C7" t="n">
-        <v>25.45180923259856</v>
+        <v>23.29589127407256</v>
       </c>
       <c r="D7" t="n">
         <v>30.78171751895449</v>
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.756567627075796</v>
+        <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.69247628885927</v>
+        <v>18.44213062427633</v>
       </c>
       <c r="D8" t="n">
-        <v>30.0414797499524</v>
+        <v>30.12492830481337</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>21.74374815365835</v>
+        <v>22.07656062539802</v>
       </c>
       <c r="D9" t="n">
-        <v>30.28593492830985</v>
+        <v>29.84218496599028</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
-        <v>21.49536598448391</v>
+        <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
-        <v>33.16834618797849</v>
+        <v>33.73775985644164</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>20.43507846389736</v>
       </c>
       <c r="D11" t="n">
-        <v>34.65078522139116</v>
+        <v>34.47308888692249</v>
       </c>
     </row>
     <row r="12">
@@ -5902,7 +5902,7 @@
         <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
-        <v>31.89403766786613</v>
+        <v>32.11100391050467</v>
       </c>
     </row>
     <row r="13">
@@ -5913,7 +5913,7 @@
         <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>19.25207248027995</v>
       </c>
       <c r="D13" t="n">
         <v>30.43908757017236</v>
@@ -5941,10 +5941,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
-        <v>27.95035713990669</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -5980,10 +5980,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.051542949202286</v>
+        <v>7.056265062905999</v>
       </c>
       <c r="C21" t="n">
-        <v>66.10821514877144</v>
+        <v>66.15248496474375</v>
       </c>
       <c r="D21" t="n">
-        <v>4.407214343251429</v>
+        <v>4.410165664316249</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.759512870188536</v>
+        <v>5.310273332270997</v>
       </c>
       <c r="C2" t="n">
-        <v>9.000662952534757</v>
+        <v>7.169703484114456</v>
       </c>
       <c r="D2" t="n">
-        <v>17.19334754447439</v>
+        <v>34.40534829532947</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.31450342272425</v>
+        <v>21.19593293468864</v>
       </c>
       <c r="C3" t="n">
-        <v>37.0904282664445</v>
+        <v>37.04624961975339</v>
       </c>
       <c r="D3" t="n">
-        <v>60.54928965942203</v>
+        <v>75.07915568227483</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.99766095615978</v>
+        <v>28.79269667015045</v>
       </c>
       <c r="C4" t="n">
-        <v>71.90516535444488</v>
+        <v>51.06364334098934</v>
       </c>
       <c r="D4" t="n">
-        <v>61.51631114810513</v>
+        <v>68.17845106912399</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26.35992585902687</v>
+        <v>26.38446955163304</v>
       </c>
       <c r="C5" t="n">
-        <v>85.80474935117124</v>
+        <v>76.55177723864504</v>
       </c>
       <c r="D5" t="n">
-        <v>39.73623832938966</v>
+        <v>45.77398671050754</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>20.68935111929729</v>
+        <v>18.91827826083604</v>
       </c>
       <c r="C6" t="n">
-        <v>91.29075552250242</v>
+        <v>69.75611962984863</v>
       </c>
       <c r="D6" t="n">
-        <v>34.45541742824607</v>
+        <v>35.46170882509904</v>
       </c>
     </row>
     <row r="7">
@@ -6137,10 +6137,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.12083708308037</v>
+        <v>9.222537933694536</v>
       </c>
       <c r="C7" t="n">
-        <v>57.49114556069321</v>
+        <v>47.13076203777662</v>
       </c>
       <c r="D7" t="n">
         <v>33.0574086973986</v>
@@ -6154,7 +6154,7 @@
         <v>5.507604620824606</v>
       </c>
       <c r="C8" t="n">
-        <v>27.70492021384499</v>
+        <v>25.95250056176443</v>
       </c>
       <c r="D8" t="n">
         <v>32.12769362147687</v>
@@ -6168,10 +6168,10 @@
         <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
-        <v>23.2968730217768</v>
+        <v>23.07499804061703</v>
       </c>
       <c r="D9" t="n">
-        <v>31.61718481526852</v>
+        <v>31.28437234352885</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>4.840016181936776</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>33.45305302221006</v>
+        <v>33.73775985644164</v>
       </c>
     </row>
     <row r="11">
@@ -6196,7 +6196,7 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.10052348092744</v>
+        <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
         <v>35.36157055926586</v>
@@ -6210,7 +6210,7 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>21.91359050649305</v>
+        <v>22.1305567491316</v>
       </c>
       <c r="D12" t="n">
         <v>33.1958351236974</v>
@@ -6238,7 +6238,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
         <v>30.11412908006666</v>
@@ -6255,7 +6255,7 @@
         <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -6280,7 +6280,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
         <v>24.0832529328785</v>
@@ -6294,10 +6294,10 @@
         <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>1.203622685406589</v>
       </c>
       <c r="C19" t="n">
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.27037755095192</v>
+        <v>7.276460916866037</v>
       </c>
       <c r="C21" t="n">
-        <v>75.43016709112618</v>
+        <v>75.49328201248514</v>
       </c>
       <c r="D21" t="n">
-        <v>5.452783163213939</v>
+        <v>5.457345687649528</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.244496236086461</v>
+        <v>4.308890673939251</v>
       </c>
       <c r="C2" t="n">
-        <v>7.116689108085128</v>
+        <v>6.510950774564847</v>
       </c>
       <c r="D2" t="n">
-        <v>17.79221364406494</v>
+        <v>38.24103657582176</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.24930716361646</v>
+        <v>19.79694245613693</v>
       </c>
       <c r="C3" t="n">
-        <v>35.83379120500858</v>
+        <v>31.56809743005618</v>
       </c>
       <c r="D3" t="n">
-        <v>60.25476534814799</v>
+        <v>85.18133955897451</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.20485077948487</v>
+        <v>35.53141291210056</v>
       </c>
       <c r="C4" t="n">
-        <v>84.05527494220341</v>
+        <v>75.19794715448869</v>
       </c>
       <c r="D4" t="n">
-        <v>78.0567964692554</v>
+        <v>90.48768590042852</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.40396563699773</v>
+        <v>35.56381058634071</v>
       </c>
       <c r="C5" t="n">
-        <v>112.2137625954105</v>
+        <v>85.85383673638358</v>
       </c>
       <c r="D5" t="n">
-        <v>52.84257018108458</v>
+        <v>59.49391087735672</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.6591789823729</v>
+        <v>27.77364255314227</v>
       </c>
       <c r="C6" t="n">
-        <v>114.9587291764845</v>
+        <v>98.41529861222153</v>
       </c>
       <c r="D6" t="n">
-        <v>38.9233512302733</v>
+        <v>42.18373535607696</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.90609637775757</v>
+        <v>16.34904451882213</v>
       </c>
       <c r="C7" t="n">
-        <v>98.0942671129328</v>
+        <v>76.53508752767283</v>
       </c>
       <c r="D7" t="n">
-        <v>35.87207936547421</v>
+        <v>36.17151241526948</v>
       </c>
     </row>
     <row r="8">
@@ -6462,10 +6462,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.428304040958867</v>
+        <v>7.927612711792993</v>
       </c>
       <c r="C8" t="n">
-        <v>53.82431788533138</v>
+        <v>45.72980806381643</v>
       </c>
       <c r="D8" t="n">
         <v>33.79666471869644</v>
@@ -6479,10 +6479,10 @@
         <v>5.546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>29.50937249425062</v>
+        <v>28.28906009787183</v>
       </c>
       <c r="D9" t="n">
-        <v>33.05937219280708</v>
+        <v>32.8374972116473</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>26.90479583488384</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>34.02246669067321</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
-        <v>35.53926689373453</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -6535,7 +6535,7 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
         <v>31.47974013667398</v>
@@ -6566,7 +6566,7 @@
         <v>19.35024725070463</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -6577,7 +6577,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>17.3592629064921</v>
       </c>
       <c r="D16" t="n">
         <v>26.03889435973815</v>
@@ -6591,7 +6591,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
         <v>24.0832529328785</v>
@@ -6608,7 +6608,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
         <v>18.82992096745382</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.475617439514187</v>
+        <v>7.483063947426261</v>
       </c>
       <c r="C21" t="n">
-        <v>84.10069619453461</v>
+        <v>84.18446940854544</v>
       </c>
       <c r="D21" t="n">
-        <v>6.541165259574914</v>
+        <v>6.547680953997978</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_31_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_31_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497634069633</v>
+        <v>10.84497633841011</v>
       </c>
       <c r="C21" t="n">
-        <v>37.7890719714623</v>
+        <v>37.78907196349603</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.506622873120359</v>
+        <v>4.631885668636452</v>
       </c>
       <c r="C2" t="n">
-        <v>6.137886646951058</v>
+        <v>6.752460709809561</v>
       </c>
       <c r="D2" t="n">
-        <v>36.70165617556276</v>
+        <v>20.89551813718911</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.20021977840412</v>
+        <v>15.85031668506475</v>
       </c>
       <c r="C3" t="n">
-        <v>28.04362317181014</v>
+        <v>40.00131020953629</v>
       </c>
       <c r="D3" t="n">
-        <v>94.58648256565895</v>
+        <v>69.1641257641878</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.53966780436203</v>
+        <v>30.78368101436299</v>
       </c>
       <c r="C4" t="n">
-        <v>76.4104055692335</v>
+        <v>75.83608316224911</v>
       </c>
       <c r="D4" t="n">
-        <v>109.491376211534</v>
+        <v>78.04403374910019</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.08047192068179</v>
+        <v>39.07355862902306</v>
       </c>
       <c r="C5" t="n">
-        <v>113.3918598405066</v>
+        <v>114.2999764669349</v>
       </c>
       <c r="D5" t="n">
-        <v>77.45989386507335</v>
+        <v>54.04521111878692</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.99756314516856</v>
+        <v>38.64158963915446</v>
       </c>
       <c r="C6" t="n">
-        <v>116.7700536908199</v>
+        <v>160.6041069377357</v>
       </c>
       <c r="D6" t="n">
-        <v>50.636583089642</v>
+        <v>41.45920555034281</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.43373686329462</v>
+        <v>27.48795397120644</v>
       </c>
       <c r="C7" t="n">
-        <v>110.0117024947848</v>
+        <v>169.658766014004</v>
       </c>
       <c r="D7" t="n">
-        <v>39.58504918293564</v>
+        <v>37.96811071404115</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.76762889372977</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>73.76852249710534</v>
+        <v>112.4052033977386</v>
       </c>
       <c r="D8" t="n">
-        <v>36.04977569994287</v>
+        <v>35.63253292563798</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.878124415953151</v>
+        <v>7.321874378272709</v>
       </c>
       <c r="C9" t="n">
-        <v>42.26718391093791</v>
+        <v>56.13437023342411</v>
       </c>
       <c r="D9" t="n">
-        <v>33.9468721174462</v>
+        <v>33.39218466454675</v>
       </c>
     </row>
     <row r="10">
@@ -892,10 +892,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.409429850399925</v>
+        <v>5.267076433284139</v>
       </c>
       <c r="C10" t="n">
-        <v>30.89069151412589</v>
+        <v>32.88363935374691</v>
       </c>
       <c r="D10" t="n">
         <v>34.73423377625215</v>
@@ -906,10 +906,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>28.96450251839364</v>
       </c>
       <c r="D11" t="n">
         <v>36.07235589714055</v>
@@ -926,7 +926,7 @@
         <v>27.55471281509523</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>34.71459882216721</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.49598787928967</v>
+        <v>25.23582473766426</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>32.5203927031756</v>
       </c>
     </row>
     <row r="14">
@@ -954,7 +954,7 @@
         <v>23.35381438862312</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -965,7 +965,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>20.42526098685489</v>
       </c>
       <c r="D15" t="n">
         <v>29.38370878810703</v>
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>18.59921025695582</v>
+        <v>19.01252604044373</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -993,7 +993,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
         <v>24.0832529328785</v>
@@ -1024,7 +1024,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.674197434128009</v>
+        <v>7.650059562063402</v>
       </c>
       <c r="C21" t="n">
-        <v>93.04964388880211</v>
+        <v>92.75697219001874</v>
       </c>
       <c r="D21" t="n">
-        <v>7.674197434128009</v>
+        <v>7.650059562063402</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.630323083855457</v>
+        <v>6.065237316836795</v>
       </c>
       <c r="C2" t="n">
-        <v>5.752059799182062</v>
+        <v>12.03917209717864</v>
       </c>
       <c r="D2" t="n">
-        <v>34.89033166122739</v>
+        <v>16.55226629360122</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.67636741496382</v>
+        <v>15.5116137270996</v>
       </c>
       <c r="C3" t="n">
-        <v>25.75615102091507</v>
+        <v>32.93272673895925</v>
       </c>
       <c r="D3" t="n">
-        <v>100.3198891584603</v>
+        <v>69.14449081010285</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.59973434077034</v>
+        <v>30.29869764846506</v>
       </c>
       <c r="C4" t="n">
-        <v>73.16867464981053</v>
+        <v>87.23319226085034</v>
       </c>
       <c r="D4" t="n">
-        <v>128.4184902017083</v>
+        <v>90.55149950120456</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.59651136021713</v>
+        <v>41.89608327873264</v>
       </c>
       <c r="C5" t="n">
-        <v>125.0746575210437</v>
+        <v>124.7310458245573</v>
       </c>
       <c r="D5" t="n">
-        <v>94.78774084502956</v>
+        <v>67.15154297048184</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>47.49695393146069</v>
+        <v>44.71958967614647</v>
       </c>
       <c r="C6" t="n">
-        <v>146.1940141348011</v>
+        <v>170.6670209062655</v>
       </c>
       <c r="D6" t="n">
-        <v>61.66553679915066</v>
+        <v>47.2956956520901</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>33.95570784678443</v>
+        <v>35.63253292563798</v>
       </c>
       <c r="C7" t="n">
-        <v>136.3618108767692</v>
+        <v>197.0868333752514</v>
       </c>
       <c r="D7" t="n">
-        <v>44.01665831990574</v>
+        <v>41.02232782195297</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>18.77592484372025</v>
+        <v>21.19593293468863</v>
       </c>
       <c r="C8" t="n">
-        <v>107.2313929963579</v>
+        <v>162.2239906497429</v>
       </c>
       <c r="D8" t="n">
-        <v>38.46978379091126</v>
+        <v>37.21805546799658</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.540624189870499</v>
+        <v>10.31718662392973</v>
       </c>
       <c r="C9" t="n">
-        <v>64.23280704575605</v>
+        <v>93.52030455884689</v>
       </c>
       <c r="D9" t="n">
-        <v>35.16718451382499</v>
+        <v>34.94530953266521</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.978843518863076</v>
+        <v>6.121196935978863</v>
       </c>
       <c r="C10" t="n">
-        <v>39.71660337530471</v>
+        <v>47.40368789955724</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>35.01894061048373</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>32.69612554223576</v>
+        <v>33.40691088011046</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>36.60544490054656</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>30.15830772675777</v>
+        <v>29.94134148411922</v>
       </c>
       <c r="D12" t="n">
-        <v>35.79943003535993</v>
+        <v>34.93156506480576</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>28.09761929554372</v>
+        <v>27.83745615391831</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>33.04071898642641</v>
       </c>
     </row>
     <row r="14">
@@ -1265,7 +1265,7 @@
         <v>25.19753657719863</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>22.21695054710532</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.83915760741954</v>
+        <v>20.25247339090745</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -1318,7 +1318,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -1335,7 +1335,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.849467794515052</v>
+        <v>7.820799635119276</v>
       </c>
       <c r="C21" t="n">
-        <v>101.0618978543813</v>
+        <v>100.6927953021607</v>
       </c>
       <c r="D21" t="n">
-        <v>8.830651268829433</v>
+        <v>8.798399589509186</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.809402076655877</v>
+        <v>8.087637587585224</v>
       </c>
       <c r="C2" t="n">
-        <v>5.479133937401449</v>
+        <v>17.59684585091983</v>
       </c>
       <c r="D2" t="n">
-        <v>35.43912862790136</v>
+        <v>19.64673505738717</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.81872083207961</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="C3" t="n">
-        <v>23.96937019918587</v>
+        <v>38.72503819401544</v>
       </c>
       <c r="D3" t="n">
-        <v>102.7938933731623</v>
+        <v>66.35141859152068</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.3489877655599</v>
+        <v>29.13729011434109</v>
       </c>
       <c r="C4" t="n">
-        <v>68.31884099083128</v>
+        <v>83.91488502049611</v>
       </c>
       <c r="D4" t="n">
-        <v>142.3426178910408</v>
+        <v>100.6468111439745</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.57825906446394</v>
+        <v>42.90237467558562</v>
       </c>
       <c r="C5" t="n">
-        <v>127.7253763225101</v>
+        <v>138.2791641431633</v>
       </c>
       <c r="D5" t="n">
-        <v>113.8091026148115</v>
+        <v>78.83434065101889</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>55.14476854754334</v>
+        <v>49.26802678992194</v>
       </c>
       <c r="C6" t="n">
-        <v>168.6544381125596</v>
+        <v>182.5010077332566</v>
       </c>
       <c r="D6" t="n">
-        <v>72.8554971321558</v>
+        <v>55.10451689166923</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>42.87881273068369</v>
+        <v>42.63926629084747</v>
       </c>
       <c r="C7" t="n">
-        <v>166.7243221260103</v>
+        <v>216.7895280517806</v>
       </c>
       <c r="D7" t="n">
-        <v>50.06520592577034</v>
+        <v>43.89688509998763</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>25.95250056176443</v>
+        <v>28.37250865273282</v>
       </c>
       <c r="C8" t="n">
-        <v>137.7735640754761</v>
+        <v>202.3627455378738</v>
       </c>
       <c r="D8" t="n">
-        <v>40.55599766243574</v>
+        <v>38.97047512007713</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>13.31249886958674</v>
+        <v>14.53281126596553</v>
       </c>
       <c r="C9" t="n">
-        <v>93.2984295776871</v>
+        <v>136.7859258850038</v>
       </c>
       <c r="D9" t="n">
-        <v>36.83124687252333</v>
+        <v>36.38749691020377</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.260024272905163</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
-        <v>54.23665192111504</v>
+        <v>72.88494956328321</v>
       </c>
       <c r="D10" t="n">
-        <v>35.87306111317846</v>
+        <v>35.44600086183109</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.153193699591506</v>
+        <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>38.02701557629594</v>
+        <v>41.5809422656694</v>
       </c>
       <c r="D11" t="n">
-        <v>36.78314123501524</v>
+        <v>36.96083756948391</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>33.1958351236974</v>
+        <v>32.97886888105885</v>
       </c>
       <c r="D12" t="n">
-        <v>35.79943003535993</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -1562,7 +1562,7 @@
         <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
-        <v>33.30088212805181</v>
+        <v>33.56104526967722</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>27.3485457972034</v>
+        <v>27.04125876577415</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>24.72531593145592</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.07910495788326</v>
+        <v>21.49242074137117</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -1615,7 +1615,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>19.36104647545135</v>
       </c>
       <c r="D17" t="n">
         <v>24.0832529328785</v>
@@ -1646,7 +1646,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.00890872682224</v>
+        <v>7.975603475417684</v>
       </c>
       <c r="C21" t="n">
-        <v>109.121381402953</v>
+        <v>107.6706469181387</v>
       </c>
       <c r="D21" t="n">
-        <v>10.0111359085278</v>
+        <v>9.969504344272105</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.243915399009714</v>
+        <v>7.267878254539137</v>
       </c>
       <c r="C2" t="n">
-        <v>3.768929436603505</v>
+        <v>12.24730261047896</v>
       </c>
       <c r="D2" t="n">
-        <v>29.33756664600743</v>
+        <v>16.35395325734337</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.15804568485051</v>
+        <v>20.238728923048</v>
       </c>
       <c r="C3" t="n">
-        <v>36.92353115672254</v>
+        <v>60.26458282519045</v>
       </c>
       <c r="D3" t="n">
-        <v>110.5644264522758</v>
+        <v>72.40389318820228</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.81523580961913</v>
+        <v>20.61179305066178</v>
       </c>
       <c r="C4" t="n">
-        <v>101.1445572300276</v>
+        <v>113.3329549782518</v>
       </c>
       <c r="D4" t="n">
-        <v>133.8171208273615</v>
+        <v>94.03572210357649</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.04777114680538</v>
+        <v>27.7343726449724</v>
       </c>
       <c r="C5" t="n">
-        <v>100.7764018409351</v>
+        <v>109.0476262492145</v>
       </c>
       <c r="D5" t="n">
-        <v>74.12195167063419</v>
+        <v>54.11884219660543</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>26.60634453279281</v>
+        <v>26.44533790929634</v>
       </c>
       <c r="C6" t="n">
-        <v>109.8065172245973</v>
+        <v>142.7726233855009</v>
       </c>
       <c r="D6" t="n">
-        <v>32.96610616090365</v>
+        <v>28.90068891761761</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.18745705824891</v>
+        <v>18.80439552714341</v>
       </c>
       <c r="C7" t="n">
-        <v>96.83664830379264</v>
+        <v>142.2905852627157</v>
       </c>
       <c r="D7" t="n">
-        <v>28.50602634051038</v>
+        <v>27.36818075128833</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.179341034707678</v>
+        <v>10.09727513817844</v>
       </c>
       <c r="C8" t="n">
-        <v>68.76160920544659</v>
+        <v>100.8058542720625</v>
       </c>
       <c r="D8" t="n">
-        <v>27.12078032981814</v>
+        <v>26.78698611037422</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>5.324999547834698</v>
       </c>
       <c r="C9" t="n">
-        <v>41.3796839862988</v>
+        <v>55.57968278052466</v>
       </c>
       <c r="D9" t="n">
-        <v>27.29062268265283</v>
+        <v>27.06874770149305</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.701188845010476</v>
+        <v>3.558835427894688</v>
       </c>
       <c r="C10" t="n">
-        <v>29.75186417719959</v>
+        <v>32.59893251951534</v>
       </c>
       <c r="D10" t="n">
-        <v>28.75539025738908</v>
+        <v>28.89774367450487</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>28.60910984945629</v>
+        <v>28.07602084605028</v>
       </c>
     </row>
     <row r="12">
@@ -1859,7 +1859,7 @@
         <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>27.12078032981814</v>
+        <v>27.33774657245668</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>22.63419332141022</v>
+        <v>22.37403017978481</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>24.97566159603886</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>20.58823110575986</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>24.89024954576939</v>
+        <v>24.58296251434014</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>21.85861263505523</v>
+        <v>22.21695054710532</v>
       </c>
     </row>
     <row r="16">
@@ -1912,7 +1912,7 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.11931555602838</v>
+        <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
         <v>20.25247339090745</v>
@@ -1943,7 +1943,7 @@
         <v>16.05157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>13.37631247036279</v>
       </c>
     </row>
     <row r="19">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
       <c r="D19" t="n">
         <v>9.027170140549421</v>
@@ -1968,7 +1968,7 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>73.30219233758808</v>
+        <v>72.62969516017901</v>
       </c>
       <c r="D20" t="n">
         <v>6.724971774090649</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.86612245932394</v>
+        <v>4.216606389740051</v>
       </c>
       <c r="C2" t="n">
-        <v>2.144136986075034</v>
+        <v>5.60479764354504</v>
       </c>
       <c r="D2" t="n">
-        <v>21.237166338267</v>
+        <v>11.5119735799981</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.44766125760332</v>
+        <v>22.88944772451438</v>
       </c>
       <c r="C3" t="n">
-        <v>26.11939767148639</v>
+        <v>55.15458602458581</v>
       </c>
       <c r="D3" t="n">
-        <v>110.1668186320558</v>
+        <v>69.54700736884405</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.09824119034946</v>
+        <v>28.12903522207961</v>
       </c>
       <c r="C4" t="n">
-        <v>100.5447093827328</v>
+        <v>134.889189320399</v>
       </c>
       <c r="D4" t="n">
-        <v>153.1526418625024</v>
+        <v>106.5431878556809</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.31208226342603</v>
+        <v>30.65507206510666</v>
       </c>
       <c r="C5" t="n">
-        <v>141.2980383337222</v>
+        <v>154.8707003449344</v>
       </c>
       <c r="D5" t="n">
-        <v>96.13764393836894</v>
+        <v>68.10874698212248</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.95981476405067</v>
+        <v>30.99377502307181</v>
       </c>
       <c r="C6" t="n">
-        <v>134.0782657166912</v>
+        <v>161.8921599257075</v>
       </c>
       <c r="D6" t="n">
-        <v>42.02272873258048</v>
+        <v>34.5359207399943</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.9897248590678</v>
+        <v>17.42700349808513</v>
       </c>
       <c r="C7" t="n">
-        <v>122.8873236359817</v>
+        <v>172.5932099019978</v>
       </c>
       <c r="D7" t="n">
-        <v>31.56024344842221</v>
+        <v>29.64387192973244</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.844164156932015</v>
+        <v>8.428304040958867</v>
       </c>
       <c r="C8" t="n">
-        <v>88.95615948180348</v>
+        <v>129.5956056991002</v>
       </c>
       <c r="D8" t="n">
-        <v>27.87181732356695</v>
+        <v>27.53802310412303</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.437499623195581</v>
+        <v>4.326562132615692</v>
       </c>
       <c r="C9" t="n">
-        <v>46.48280855297372</v>
+        <v>59.57343244140068</v>
       </c>
       <c r="D9" t="n">
-        <v>28.28906009787183</v>
+        <v>28.39999758845172</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>32.31422568528377</v>
+        <v>33.88011327355743</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>29.60951076008381</v>
       </c>
     </row>
     <row r="11">
@@ -2153,10 +2153,10 @@
         <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
+        <v>29.14219885286231</v>
+      </c>
+      <c r="D11" t="n">
         <v>29.31989518733098</v>
-      </c>
-      <c r="D11" t="n">
-        <v>29.67528785626833</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>20.61179305066178</v>
+        <v>20.39482680802324</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>28.20561154301086</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.91060420565131</v>
+        <v>16.3902779224005</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>14.74977750860408</v>
+        <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>18.12993485432585</v>
+        <v>18.4372218857551</v>
       </c>
     </row>
     <row r="15">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>13.97517856995334</v>
       </c>
       <c r="D15" t="n">
         <v>17.20021977840412</v>
@@ -2240,7 +2240,7 @@
         <v>13.69439872653876</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>11.33329549782518</v>
       </c>
     </row>
     <row r="18">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>13.9113649691773</v>
+        <v>14.44641746799181</v>
       </c>
       <c r="D18" t="n">
         <v>7.490734983403163</v>
@@ -2265,7 +2265,7 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>63.79200232654924</v>
+        <v>63.19019098384595</v>
       </c>
       <c r="D19" t="n">
         <v>5.416302084329653</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.336379609658161</v>
+        <v>3.791509633801182</v>
       </c>
       <c r="C2" t="n">
-        <v>8.003207285019998</v>
+        <v>10.19937689942011</v>
       </c>
       <c r="D2" t="n">
-        <v>21.29705294822606</v>
+        <v>15.48510653908494</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.7745421853885</v>
+        <v>18.61393647251952</v>
       </c>
       <c r="C3" t="n">
-        <v>16.66025854106837</v>
+        <v>38.20962064928586</v>
       </c>
       <c r="D3" t="n">
-        <v>102.2195709661779</v>
+        <v>63.23927836905829</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.33095645398497</v>
+        <v>35.37826027023806</v>
       </c>
       <c r="C4" t="n">
-        <v>83.4299016545982</v>
+        <v>136.0761222948334</v>
       </c>
       <c r="D4" t="n">
-        <v>170.2419241503267</v>
+        <v>115.426041083706</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.57072387799944</v>
+        <v>35.7356164345839</v>
       </c>
       <c r="C5" t="n">
-        <v>162.3319828972101</v>
+        <v>198.8039101099791</v>
       </c>
       <c r="D5" t="n">
-        <v>123.675667042492</v>
+        <v>87.03193398147975</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.23907308041327</v>
+        <v>35.54221213684728</v>
       </c>
       <c r="C6" t="n">
-        <v>177.1877891578729</v>
+        <v>201.7412992410856</v>
       </c>
       <c r="D6" t="n">
-        <v>58.08313942635406</v>
+        <v>45.16235789076178</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.67328330313084</v>
+        <v>24.91282974296706</v>
       </c>
       <c r="C7" t="n">
-        <v>155.1063197939536</v>
+        <v>200.6201433628357</v>
       </c>
       <c r="D7" t="n">
-        <v>35.45287309576081</v>
+        <v>32.27888276793088</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.26555490623215</v>
+        <v>12.01659189998096</v>
       </c>
       <c r="C8" t="n">
-        <v>122.8362727553609</v>
+        <v>174.2405825497239</v>
       </c>
       <c r="D8" t="n">
-        <v>29.6242369756475</v>
+        <v>29.2069942013426</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.546874528994477</v>
+        <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>73.99530621678632</v>
+        <v>101.5078038805989</v>
       </c>
       <c r="D9" t="n">
-        <v>29.28749751309084</v>
+        <v>28.95468504135117</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.562361508084175</v>
+        <v>2.420008090968388</v>
       </c>
       <c r="C10" t="n">
-        <v>41.70955121492574</v>
+        <v>47.83074815090461</v>
       </c>
       <c r="D10" t="n">
-        <v>30.32127784566274</v>
+        <v>30.17892442854695</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>33.22921454564179</v>
+        <v>33.40691088011046</v>
       </c>
       <c r="D11" t="n">
-        <v>30.20837685967435</v>
+        <v>29.49759152179966</v>
       </c>
     </row>
     <row r="12">
@@ -2478,7 +2478,7 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>25.16808414607123</v>
+        <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
         <v>28.8565102709265</v>
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>18.47158305540374</v>
       </c>
       <c r="D13" t="n">
-        <v>26.79680358741669</v>
+        <v>26.01631416254048</v>
       </c>
     </row>
     <row r="14">
@@ -2509,7 +2509,7 @@
         <v>15.97892563432109</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>19.0517959486136</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.0501923061036</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>16.84188186635403</v>
       </c>
     </row>
     <row r="16">
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.46605242207675</v>
+        <v>14.05273663858884</v>
       </c>
       <c r="D16" t="n">
         <v>14.46605242207675</v>
@@ -2551,7 +2551,7 @@
         <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>10.38885420633975</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.3032465340878</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
         <v>3.610868056219768</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.59475918232432</v>
+        <v>2.295326132529043</v>
       </c>
       <c r="C2" t="n">
-        <v>3.732604771546373</v>
+        <v>4.916592502868026</v>
       </c>
       <c r="D2" t="n">
-        <v>14.86366024229671</v>
+        <v>10.80020649441916</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.02979658849267</v>
+        <v>18.04943154257761</v>
       </c>
       <c r="C3" t="n">
-        <v>23.99882263031328</v>
+        <v>41.25794727097221</v>
       </c>
       <c r="D3" t="n">
-        <v>100.3689765436727</v>
+        <v>63.29327449279187</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.00661985868502</v>
+        <v>38.86248287260999</v>
       </c>
       <c r="C4" t="n">
-        <v>77.40589774133977</v>
+        <v>135.0168165219511</v>
       </c>
       <c r="D4" t="n">
-        <v>182.0984911745154</v>
+        <v>122.5476389303124</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.67519004527711</v>
+        <v>37.35550014659114</v>
       </c>
       <c r="C5" t="n">
-        <v>186.7284133477434</v>
+        <v>244.9951395947916</v>
       </c>
       <c r="D5" t="n">
-        <v>130.7687942056752</v>
+        <v>91.49888603580274</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.83276839957533</v>
+        <v>29.26295382048468</v>
       </c>
       <c r="C6" t="n">
-        <v>209.7111271041612</v>
+        <v>236.1967166693317</v>
       </c>
       <c r="D6" t="n">
-        <v>56.47307319138928</v>
+        <v>44.23656980565704</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.425939634922873</v>
+        <v>7.964919124554372</v>
       </c>
       <c r="C7" t="n">
-        <v>161.3944138396544</v>
+        <v>216.7296414418216</v>
       </c>
       <c r="D7" t="n">
-        <v>35.2133266559246</v>
+        <v>32.75797564760332</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.838633523605028</v>
+        <v>3.922082078466008</v>
       </c>
       <c r="C8" t="n">
-        <v>91.79341034707677</v>
+        <v>124.3383467428585</v>
       </c>
       <c r="D8" t="n">
-        <v>31.29320807286708</v>
+        <v>30.95941385342316</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>1.664062358698343</v>
       </c>
       <c r="C9" t="n">
-        <v>31.8390597964283</v>
+        <v>36.49843440078366</v>
       </c>
       <c r="D9" t="n">
-        <v>31.72812230584841</v>
+        <v>31.50624732468863</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>26.05067533218912</v>
+        <v>26.1930287493049</v>
       </c>
       <c r="D10" t="n">
-        <v>23.63066724122073</v>
+        <v>23.06125357275758</v>
       </c>
     </row>
     <row r="11">
@@ -2775,7 +2775,7 @@
         <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>20.07968579496001</v>
+        <v>19.72429312602266</v>
       </c>
       <c r="D11" t="n">
         <v>23.10052348092744</v>
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.4046032273367</v>
+        <v>14.97067074205961</v>
       </c>
       <c r="D12" t="n">
-        <v>21.69662426385451</v>
+        <v>21.26269177857742</v>
       </c>
     </row>
     <row r="13">
@@ -2806,7 +2806,7 @@
         <v>13.00815708127024</v>
       </c>
       <c r="D13" t="n">
-        <v>15.34962535589888</v>
+        <v>15.60978849752428</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.59876828859932</v>
+        <v>13.21334235145782</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>14.13520344574558</v>
       </c>
     </row>
     <row r="15">
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.18348900970292</v>
+        <v>11.82515109765283</v>
       </c>
       <c r="D15" t="n">
         <v>12.18348900970292</v>
@@ -2848,7 +2848,7 @@
         <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>8.679631453246051</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.27768003604838</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.42788743479814</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="D18" t="n">
         <v>2.675262494072558</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.100359250011427</v>
+        <v>2.418044595559894</v>
       </c>
       <c r="C2" t="n">
-        <v>7.37488875430204</v>
+        <v>7.932521450314227</v>
       </c>
       <c r="D2" t="n">
-        <v>13.41656412623691</v>
+        <v>10.66767055434584</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.62174939642449</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="C3" t="n">
-        <v>19.21280257211008</v>
+        <v>30.42927009312989</v>
       </c>
       <c r="D3" t="n">
-        <v>91.04237335332796</v>
+        <v>57.94765824316799</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.27539774547039</v>
+        <v>36.64176956560371</v>
       </c>
       <c r="C4" t="n">
-        <v>69.46748580480005</v>
+        <v>119.6887896155456</v>
       </c>
       <c r="D4" t="n">
-        <v>188.6712920544478</v>
+        <v>125.2660983233718</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.06913291658734</v>
+        <v>45.79853040311371</v>
       </c>
       <c r="C5" t="n">
-        <v>167.9034011188108</v>
+        <v>248.5785187152924</v>
       </c>
       <c r="D5" t="n">
-        <v>158.3804483876167</v>
+        <v>109.4648690235194</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.37241084174159</v>
+        <v>37.23278168356029</v>
       </c>
       <c r="C6" t="n">
-        <v>249.7212730430358</v>
+        <v>303.1754720438661</v>
       </c>
       <c r="D6" t="n">
-        <v>76.96116603131597</v>
+        <v>58.28439770572465</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.82813739849458</v>
+        <v>15.92983824910874</v>
       </c>
       <c r="C7" t="n">
-        <v>221.9397765082594</v>
+        <v>272.3643020937841</v>
       </c>
       <c r="D7" t="n">
-        <v>41.3816474817073</v>
+        <v>36.29128563518759</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.006913291658733</v>
+        <v>5.17381040138069</v>
       </c>
       <c r="C8" t="n">
-        <v>142.6970288122739</v>
+        <v>187.5923513274805</v>
       </c>
       <c r="D8" t="n">
-        <v>33.12907627980861</v>
+        <v>32.46148784092078</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.218749811597791</v>
+        <v>1.996874830438012</v>
       </c>
       <c r="C9" t="n">
-        <v>60.68280734719958</v>
+        <v>76.65780599070366</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>32.28280975874785</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>31.03304493124168</v>
+        <v>32.45657910239955</v>
       </c>
       <c r="D10" t="n">
-        <v>24.91184799526281</v>
+        <v>24.34243432679967</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>23.63361248433346</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.57426565372215</v>
+        <v>17.14033316844506</v>
       </c>
       <c r="D12" t="n">
-        <v>21.91359050649305</v>
+        <v>21.26269177857742</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>15.08946221427348</v>
+        <v>14.82929907264807</v>
       </c>
       <c r="D13" t="n">
-        <v>15.34962535589888</v>
+        <v>15.60978849752428</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>13.82791641431633</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>13.82791641431633</v>
       </c>
     </row>
     <row r="15">
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.25850274585317</v>
+        <v>12.90016483380309</v>
       </c>
       <c r="D15" t="n">
         <v>11.46681318560274</v>
@@ -3156,10 +3156,10 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>23.97231544229862</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>7.852999886270235</v>
       </c>
     </row>
     <row r="17">
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.52766584773283</v>
+        <v>33.0554452019901</v>
       </c>
       <c r="D17" t="n">
         <v>4.249985811684442</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.069524160552276</v>
+        <v>1.645409152317654</v>
       </c>
       <c r="C2" t="n">
-        <v>4.225442119078272</v>
+        <v>4.130212591766331</v>
       </c>
       <c r="D2" t="n">
-        <v>9.919578803709772</v>
+        <v>7.595781987757572</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.46328710541326</v>
+        <v>11.32936850700819</v>
       </c>
       <c r="C3" t="n">
-        <v>23.67484588791183</v>
+        <v>30.85142160595602</v>
       </c>
       <c r="D3" t="n">
-        <v>83.21293541195965</v>
+        <v>54.36918786118836</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.48486985937346</v>
+        <v>33.1958351236974</v>
       </c>
       <c r="C4" t="n">
-        <v>62.15444715586556</v>
+        <v>105.0627123176767</v>
       </c>
       <c r="D4" t="n">
-        <v>193.0106169072187</v>
+        <v>125.8276580102009</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>54.04521111878692</v>
+        <v>49.65189014228245</v>
       </c>
       <c r="C5" t="n">
-        <v>157.0550889868835</v>
+        <v>244.3815472796373</v>
       </c>
       <c r="D5" t="n">
-        <v>176.6654993792135</v>
+        <v>122.1048707156971</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>47.97997380195012</v>
+        <v>42.98876847355934</v>
       </c>
       <c r="C6" t="n">
-        <v>270.5716307858295</v>
+        <v>346.1642405174254</v>
       </c>
       <c r="D6" t="n">
-        <v>94.06811977781665</v>
+        <v>68.0252984272615</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.15131231964102</v>
+        <v>14.19312656029614</v>
       </c>
       <c r="C7" t="n">
-        <v>270.0287243053809</v>
+        <v>331.1729530735765</v>
       </c>
       <c r="D7" t="n">
-        <v>46.41212271826796</v>
+        <v>40.12402867256714</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.088979188187965</v>
+        <v>4.172427743048944</v>
       </c>
       <c r="C8" t="n">
-        <v>184.9219975719292</v>
+        <v>234.3235420496287</v>
       </c>
       <c r="D8" t="n">
-        <v>34.21390749300134</v>
+        <v>33.71321616383547</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.664062358698343</v>
+        <v>1.553124868118454</v>
       </c>
       <c r="C9" t="n">
-        <v>69.11405663127118</v>
+        <v>83.09218044433726</v>
       </c>
       <c r="D9" t="n">
-        <v>32.39374724932775</v>
+        <v>31.94999728700819</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>31.74481201682062</v>
+        <v>32.31422568528377</v>
       </c>
       <c r="D10" t="n">
-        <v>25.33890824661018</v>
+        <v>24.91184799526281</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>22.38973814305275</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.70640068316797</v>
+        <v>16.27246819789088</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>19.7439280801076</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.18701508989241</v>
+        <v>11.44717823151781</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>15.60978849752428</v>
       </c>
     </row>
     <row r="14">
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06233313145306</v>
+        <v>10.75504610002381</v>
       </c>
       <c r="D14" t="n">
         <v>10.75504610002381</v>
@@ -3453,10 +3453,10 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>20.0669230748048</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>6.450082416901544</v>
       </c>
     </row>
     <row r="16">
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.51878906066559</v>
+        <v>28.10547327717769</v>
       </c>
       <c r="D16" t="n">
         <v>3.306526267903257</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.353650157707104</v>
+        <v>2.190279128174634</v>
       </c>
       <c r="C2" t="n">
-        <v>12.49961177047039</v>
+        <v>9.804714322312895</v>
       </c>
       <c r="D2" t="n">
-        <v>15.21905291123405</v>
+        <v>15.02270337038469</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.856746950637977</v>
+        <v>8.673740967020569</v>
       </c>
       <c r="C3" t="n">
-        <v>20.16018910670825</v>
+        <v>24.1166323548229</v>
       </c>
       <c r="D3" t="n">
-        <v>73.85197105196632</v>
+        <v>49.13647259755286</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.62227348023901</v>
+        <v>28.03969618099315</v>
       </c>
       <c r="C4" t="n">
-        <v>60.59739529693012</v>
+        <v>92.84878912914209</v>
       </c>
       <c r="D4" t="n">
-        <v>190.4963610366426</v>
+        <v>124.0791653489374</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>53.08800710714628</v>
+        <v>49.43099690882691</v>
       </c>
       <c r="C5" t="n">
-        <v>138.6473195322558</v>
+        <v>223.0285347122692</v>
       </c>
       <c r="D5" t="n">
-        <v>197.4294633240336</v>
+        <v>132.1677846842269</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>57.27810630887167</v>
+        <v>51.20010627187966</v>
       </c>
       <c r="C6" t="n">
-        <v>263.2860810726139</v>
+        <v>363.3114459198002</v>
       </c>
       <c r="D6" t="n">
-        <v>117.2530735613093</v>
+        <v>83.64294090641977</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>28.92523261022377</v>
+        <v>25.45180923259856</v>
       </c>
       <c r="C7" t="n">
-        <v>319.2555176917245</v>
+        <v>399.1442553771044</v>
       </c>
       <c r="D7" t="n">
-        <v>56.89227946110266</v>
+        <v>46.8912155979404</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.844164156932015</v>
+        <v>7.260024272905162</v>
       </c>
       <c r="C8" t="n">
-        <v>254.1008495516807</v>
+        <v>307.6748217724291</v>
       </c>
       <c r="D8" t="n">
-        <v>37.1346069131356</v>
+        <v>35.71598148049896</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>2.218749811597791</v>
       </c>
       <c r="C9" t="n">
-        <v>126.9124892233936</v>
+        <v>153.2046744908274</v>
       </c>
       <c r="D9" t="n">
-        <v>33.28124717396686</v>
+        <v>32.8374972116473</v>
       </c>
     </row>
     <row r="10">
@@ -3694,10 +3694,10 @@
         <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>48.68486865359933</v>
+        <v>52.95547116707295</v>
       </c>
       <c r="D10" t="n">
-        <v>26.47773558353648</v>
+        <v>26.1930287493049</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.72062817711293</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>24.6997904911455</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>18.87606310955342</v>
       </c>
       <c r="D12" t="n">
-        <v>20.39482680802324</v>
+        <v>20.17786056538469</v>
       </c>
     </row>
     <row r="13">
@@ -3739,7 +3739,7 @@
         <v>13.00815708127024</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.67690719431156</v>
+        <v>11.36962016288231</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>10.75504610002381</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>6.091744504851459</v>
       </c>
     </row>
     <row r="16">
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>27.69215749368978</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
         <v>2.89321048441535</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.220533380557038</v>
+        <v>5.533130061135023</v>
       </c>
       <c r="C2" t="n">
-        <v>7.994371555681777</v>
+        <v>13.8799490426414</v>
       </c>
       <c r="D2" t="n">
-        <v>10.35743827980385</v>
+        <v>7.119634351197869</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.397427893770711</v>
+        <v>1.61890196430299</v>
       </c>
       <c r="C2" t="n">
-        <v>7.200137662946108</v>
+        <v>5.805074175211389</v>
       </c>
       <c r="D2" t="n">
-        <v>11.20075955775186</v>
+        <v>11.17621586514569</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.55793579564845</v>
+        <v>11.76624623539802</v>
       </c>
       <c r="C3" t="n">
-        <v>31.41592653589793</v>
+        <v>32.18168974521045</v>
       </c>
       <c r="D3" t="n">
-        <v>80.68984381204535</v>
+        <v>55.04168503859743</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.63650097418398</v>
+        <v>38.08395694314227</v>
       </c>
       <c r="C4" t="n">
-        <v>86.03349656626072</v>
+        <v>131.1241868746125</v>
       </c>
       <c r="D4" t="n">
-        <v>194.7080586878614</v>
+        <v>126.7338111412208</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.23215978875454</v>
+        <v>28.83883881225006</v>
       </c>
       <c r="C5" t="n">
-        <v>215.0272909226577</v>
+        <v>319.3625281914875</v>
       </c>
       <c r="D5" t="n">
-        <v>177.1809169239431</v>
+        <v>119.3805208364122</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>17.95223851985718</v>
+        <v>15.77864910265474</v>
       </c>
       <c r="C6" t="n">
-        <v>261.8772731170197</v>
+        <v>323.4220549485481</v>
       </c>
       <c r="D6" t="n">
-        <v>90.04295419040471</v>
+        <v>67.34102027740147</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.150248456478767</v>
+        <v>4.790928796724434</v>
       </c>
       <c r="C7" t="n">
-        <v>178.7016441178214</v>
+        <v>216.3703217820673</v>
       </c>
       <c r="D7" t="n">
-        <v>33.35684174719388</v>
+        <v>30.60205768907732</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.585522542358599</v>
+        <v>1.50207398749762</v>
       </c>
       <c r="C8" t="n">
-        <v>93.54582999915733</v>
+        <v>112.9058947269044</v>
       </c>
       <c r="D8" t="n">
-        <v>24.53387512912779</v>
+        <v>24.20008090968387</v>
       </c>
     </row>
     <row r="9">
@@ -4302,10 +4302,10 @@
         <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>37.16405934426299</v>
+        <v>40.38124657107979</v>
       </c>
       <c r="D9" t="n">
-        <v>20.1906232855399</v>
+        <v>19.96874830438012</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>21.6377194015997</v>
+        <v>20.92595231602077</v>
       </c>
       <c r="D10" t="n">
-        <v>19.3600647277471</v>
+        <v>18.93300447639974</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.81497376771187</v>
+        <v>15.10418842983717</v>
       </c>
       <c r="D11" t="n">
-        <v>16.34806277111788</v>
+        <v>16.17036643664921</v>
       </c>
     </row>
     <row r="12">
@@ -4347,7 +4347,7 @@
         <v>10.63134588928871</v>
       </c>
       <c r="D12" t="n">
-        <v>13.23494080095125</v>
+        <v>12.80100831567416</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.626036240139976</v>
+        <v>9.365873098514571</v>
       </c>
       <c r="D13" t="n">
-        <v>9.105709956889166</v>
+        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>16.90078672860884</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>4.916592502868027</v>
       </c>
     </row>
     <row r="15">
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>22.21695054710532</v>
       </c>
       <c r="D15" t="n">
         <v>2.150027472300515</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.820782138479339</v>
+        <v>7.15301377314226</v>
       </c>
       <c r="C2" t="n">
-        <v>5.253331965424683</v>
+        <v>8.995754214013523</v>
       </c>
       <c r="D2" t="n">
-        <v>24.03514729537041</v>
+        <v>11.97241325328985</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>8.973174016815847</v>
+        <v>11.75642875835555</v>
       </c>
       <c r="C3" t="n">
-        <v>20.14546289114455</v>
+        <v>34.97476196379262</v>
       </c>
       <c r="D3" t="n">
-        <v>11.8349685746953</v>
+        <v>9.115527433931634</v>
       </c>
     </row>
     <row r="4">
@@ -4554,7 +4554,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>4.736932672990861</v>
       </c>
       <c r="C5" t="n">
         <v>9.35114688295087</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
         <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>32.8453511932813</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>32.21899615797182</v>
       </c>
     </row>
     <row r="8">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39812685213415</v>
+        <v>13.39744738623795</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14313469646703</v>
+        <v>70.13957749265748</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576250217898135</v>
+        <v>1.576170280733876</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.483641765295182</v>
+        <v>4.802709769175396</v>
       </c>
       <c r="C2" t="n">
-        <v>5.361324212891832</v>
+        <v>9.353110378359363</v>
       </c>
       <c r="D2" t="n">
-        <v>25.19360958638165</v>
+        <v>15.02957560431442</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.61960597456675</v>
+        <v>19.49750940634166</v>
       </c>
       <c r="C3" t="n">
-        <v>20.35653864755761</v>
+        <v>35.0434843030899</v>
       </c>
       <c r="D3" t="n">
-        <v>29.1628155546515</v>
+        <v>16.96950906790612</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>10.56753228851267</v>
+        <v>13.71992416684918</v>
       </c>
       <c r="C4" t="n">
-        <v>31.2559016601057</v>
+        <v>53.8331536146696</v>
       </c>
       <c r="D4" t="n">
-        <v>21.27545449873262</v>
+        <v>19.84602984134927</v>
       </c>
     </row>
     <row r="5">
@@ -4865,10 +4865,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.043417883165113</v>
+        <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.375068680751288</v>
+        <v>5.473243451175969</v>
       </c>
       <c r="D5" t="n">
         <v>29.40334374219198</v>
@@ -4882,10 +4882,10 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.50317890838889</v>
+        <v>16.34217228489241</v>
       </c>
       <c r="D6" t="n">
-        <v>34.3346624606237</v>
+        <v>34.57617239586842</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>34.97378021608837</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -4952,7 +4952,7 @@
         <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
         <v>47.97801030654161</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>28.8565102709265</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5025,7 +5025,7 @@
         <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>31.63878326476196</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>36.36098972218912</v>
       </c>
     </row>
     <row r="18">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43988209032375</v>
+        <v>15.43764170860733</v>
       </c>
       <c r="C21" t="n">
-        <v>86.13828955654303</v>
+        <v>86.12579058486195</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250501492699737</v>
+        <v>3.250029833391017</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.837070938824034</v>
+        <v>3.960370238931633</v>
       </c>
       <c r="C2" t="n">
-        <v>7.966882619962866</v>
+        <v>7.117670855789376</v>
       </c>
       <c r="D2" t="n">
-        <v>21.5601613329642</v>
+        <v>16.69265621530852</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.57051858935441</v>
+        <v>18.04943154257761</v>
       </c>
       <c r="C3" t="n">
-        <v>20.66088043587412</v>
+        <v>35.82397372796611</v>
       </c>
       <c r="D3" t="n">
-        <v>42.54894550205677</v>
+        <v>25.0542014123786</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.72214970416493</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="C4" t="n">
-        <v>42.86997700134547</v>
+        <v>73.46221721338033</v>
       </c>
       <c r="D4" t="n">
-        <v>31.08998629808799</v>
+        <v>23.89181213055038</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>9.645671194224914</v>
+        <v>12.10004045484194</v>
       </c>
       <c r="C5" t="n">
-        <v>35.19565519724816</v>
+        <v>57.99674562838034</v>
       </c>
       <c r="D5" t="n">
-        <v>30.31146036862028</v>
+        <v>29.82058651649687</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>5.916993413495527</v>
       </c>
       <c r="C6" t="n">
         <v>12.23650338573225</v>
       </c>
       <c r="D6" t="n">
-        <v>36.34724525432967</v>
+        <v>36.54850353370026</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.521970983489814</v>
       </c>
       <c r="C7" t="n">
-        <v>24.25407703341745</v>
+        <v>24.37385025333556</v>
       </c>
       <c r="D7" t="n">
-        <v>37.66867766424586</v>
+        <v>37.4890178343687</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>10.34762080276138</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>29.54078842078653</v>
       </c>
       <c r="D8" t="n">
-        <v>38.05254101660637</v>
+        <v>37.88564390688441</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
         <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>41.15780900513902</v>
       </c>
     </row>
     <row r="10">
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.174031385558941</v>
+        <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>30.91916219754903</v>
+        <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5277,7 +5277,7 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>31.89403766786613</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D12" t="n">
         <v>46.2138096820101</v>
@@ -5291,7 +5291,7 @@
         <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>29.91876128692155</v>
       </c>
       <c r="D13" t="n">
         <v>45.00822350119503</v>
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>27.23368131580652</v>
+        <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>43.71722527011046</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
         <v>40.91826256530281</v>
@@ -5350,7 +5350,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73175065010522</v>
+        <v>16.72464595942436</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0636789656418</v>
+        <v>102.0203403524886</v>
       </c>
       <c r="D21" t="n">
-        <v>4.182937662526304</v>
+        <v>4.18116148985609</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.465790380169493</v>
+        <v>4.687845287778519</v>
       </c>
       <c r="C2" t="n">
-        <v>4.885176576332128</v>
+        <v>4.487568756112171</v>
       </c>
       <c r="D2" t="n">
-        <v>27.84040139703105</v>
+        <v>24.72727942686441</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.12029730373262</v>
+        <v>15.59015354343935</v>
       </c>
       <c r="C3" t="n">
-        <v>26.57100161543993</v>
+        <v>31.13121970166636</v>
       </c>
       <c r="D3" t="n">
-        <v>49.47026681699678</v>
+        <v>32.16696352964674</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.38054256081604</v>
+        <v>31.23037621979529</v>
       </c>
       <c r="C4" t="n">
-        <v>47.80914970141117</v>
+        <v>82.31954500109505</v>
       </c>
       <c r="D4" t="n">
-        <v>44.64399510291945</v>
+        <v>30.68157925312132</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>20.98485717827558</v>
+        <v>25.77087723647878</v>
       </c>
       <c r="C5" t="n">
-        <v>58.61033794353459</v>
+        <v>98.59201319898595</v>
       </c>
       <c r="D5" t="n">
-        <v>34.18936380039518</v>
+        <v>31.39138284329177</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>9.620145753914496</v>
+        <v>11.10945702125691</v>
       </c>
       <c r="C6" t="n">
-        <v>35.22019888985433</v>
+        <v>53.45419900083034</v>
       </c>
       <c r="D6" t="n">
-        <v>38.11831811279092</v>
+        <v>38.15856976866503</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>8.563785224144926</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>21.31963314542373</v>
       </c>
       <c r="D7" t="n">
-        <v>39.64493579289469</v>
+        <v>39.88448223273092</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>10.6814150222053</v>
       </c>
       <c r="C8" t="n">
-        <v>31.37665662772806</v>
+        <v>31.29320807286708</v>
       </c>
       <c r="D8" t="n">
-        <v>40.05530633326986</v>
+        <v>39.30426933952106</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>34.39062207976576</v>
+        <v>34.05780960802609</v>
       </c>
       <c r="D9" t="n">
-        <v>41.82343394861835</v>
+        <v>42.15624642035802</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.59540643932586</v>
+        <v>33.45305302221006</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>48.68486865359933</v>
       </c>
     </row>
     <row r="11">
@@ -5571,10 +5571,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.707120388964958</v>
+        <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.22921454564179</v>
+        <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
         <v>50.82115165804038</v>
@@ -5585,7 +5585,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>7.159886007071988</v>
       </c>
       <c r="C12" t="n">
         <v>34.28066633689012</v>
@@ -5602,7 +5602,7 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>32.5203927031756</v>
       </c>
       <c r="D13" t="n">
         <v>45.78871292607123</v>
@@ -5616,10 +5616,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>45.7857676829585</v>
       </c>
     </row>
     <row r="15">
@@ -5630,7 +5630,7 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.02537087605695</v>
+        <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
         <v>43.71722527011046</v>
@@ -5644,7 +5644,7 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
         <v>41.33157834879071</v>
@@ -5658,10 +5658,10 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5689,7 +5689,7 @@
         <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>25.27607639353838</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>39.67733346713483</v>
       </c>
       <c r="D20" t="n">
         <v>16.13993225781756</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.05617543183745</v>
+        <v>18.03915952918638</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7950492457967</v>
+        <v>117.6840407380254</v>
       </c>
       <c r="D21" t="n">
-        <v>6.018725143945816</v>
+        <v>6.013053176395459</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.776022654711485</v>
+        <v>5.488951414443917</v>
       </c>
       <c r="C2" t="n">
-        <v>11.76035574917254</v>
+        <v>7.667449570167589</v>
       </c>
       <c r="D2" t="n">
-        <v>38.73780091417064</v>
+        <v>26.76538766088079</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.37693436516854</v>
+        <v>14.02917469368692</v>
       </c>
       <c r="C3" t="n">
-        <v>20.86704745376596</v>
+        <v>22.21695054710532</v>
       </c>
       <c r="D3" t="n">
-        <v>56.09706382066275</v>
+        <v>40.51181901574463</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.04572553593887</v>
+        <v>22.04121770804514</v>
       </c>
       <c r="C4" t="n">
-        <v>48.76635371305181</v>
+        <v>66.03431408304895</v>
       </c>
       <c r="D4" t="n">
-        <v>51.12745694176539</v>
+        <v>33.61700488881928</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>18.70229376590174</v>
+        <v>22.23658550119026</v>
       </c>
       <c r="C5" t="n">
-        <v>54.97787143782139</v>
+        <v>94.05143006684445</v>
       </c>
       <c r="D5" t="n">
-        <v>33.79666471869646</v>
+        <v>28.49522711576368</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.34467555964864</v>
+        <v>12.31700669748049</v>
       </c>
       <c r="C6" t="n">
-        <v>44.39757642915352</v>
+        <v>70.88316599432396</v>
       </c>
       <c r="D6" t="n">
-        <v>31.31578827006476</v>
+        <v>30.3497485290859</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.090361846519712</v>
+        <v>5.449681506274044</v>
       </c>
       <c r="C7" t="n">
-        <v>23.29589127407256</v>
+        <v>31.38058361854505</v>
       </c>
       <c r="D7" t="n">
-        <v>30.78171751895449</v>
+        <v>31.26081039862693</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>4.756567627075796</v>
       </c>
       <c r="C8" t="n">
         <v>18.44213062427633</v>
       </c>
       <c r="D8" t="n">
-        <v>30.12492830481337</v>
+        <v>29.37389131106456</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>4.77031209493525</v>
       </c>
       <c r="C9" t="n">
-        <v>22.07656062539802</v>
+        <v>21.85468564423824</v>
       </c>
       <c r="D9" t="n">
-        <v>29.84218496599028</v>
+        <v>30.17499743772996</v>
       </c>
     </row>
     <row r="10">
@@ -5871,10 +5871,10 @@
         <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>21.21065915025234</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>33.16834618797849</v>
       </c>
     </row>
     <row r="11">
@@ -5888,7 +5888,7 @@
         <v>20.43507846389736</v>
       </c>
       <c r="D11" t="n">
-        <v>34.47308888692249</v>
+        <v>34.65078522139116</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>2.820561154301086</v>
       </c>
       <c r="C12" t="n">
         <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
-        <v>32.11100391050467</v>
+        <v>31.89403766786613</v>
       </c>
     </row>
     <row r="13">
@@ -5913,7 +5913,7 @@
         <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
         <v>30.43908757017236</v>
@@ -5927,7 +5927,7 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
         <v>29.49955501720816</v>
@@ -5941,7 +5941,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -5958,7 +5958,7 @@
         <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -5969,10 +5969,10 @@
         <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>23.13881164139307</v>
       </c>
     </row>
     <row r="18">
@@ -5980,7 +5980,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.605157496443535</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
         <v>17.65673246087889</v>
@@ -6011,7 +6011,7 @@
         <v>1.34499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.08745766113597</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.056265062905999</v>
+        <v>7.044646155996231</v>
       </c>
       <c r="C21" t="n">
-        <v>66.15248496474375</v>
+        <v>66.04355771246466</v>
       </c>
       <c r="D21" t="n">
-        <v>4.410165664316249</v>
+        <v>4.402903847497645</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.310273332270997</v>
+        <v>4.578871292607124</v>
       </c>
       <c r="C2" t="n">
-        <v>7.169703484114456</v>
+        <v>10.48997421987717</v>
       </c>
       <c r="D2" t="n">
-        <v>34.40534829532947</v>
+        <v>29.89716283742811</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.19593293468864</v>
+        <v>17.15113239319178</v>
       </c>
       <c r="C3" t="n">
-        <v>37.04624961975339</v>
+        <v>27.1158715912969</v>
       </c>
       <c r="D3" t="n">
-        <v>75.07915568227483</v>
+        <v>53.20581683165589</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.79269667015045</v>
+        <v>25.53820303057228</v>
       </c>
       <c r="C4" t="n">
-        <v>51.06364334098934</v>
+        <v>59.72953032637594</v>
       </c>
       <c r="D4" t="n">
-        <v>68.17845106912399</v>
+        <v>47.04338649209866</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26.38446955163304</v>
+        <v>28.74066404182538</v>
       </c>
       <c r="C5" t="n">
-        <v>76.55177723864504</v>
+        <v>111.0602090429204</v>
       </c>
       <c r="D5" t="n">
-        <v>45.77398671050754</v>
+        <v>34.28753857081986</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>18.91827826083604</v>
+        <v>22.1786623866397</v>
       </c>
       <c r="C6" t="n">
-        <v>69.75611962984863</v>
+        <v>116.448040443827</v>
       </c>
       <c r="D6" t="n">
-        <v>35.46170882509904</v>
+        <v>33.04660947265189</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.222537933694536</v>
+        <v>10.71970318267092</v>
       </c>
       <c r="C7" t="n">
-        <v>47.13076203777662</v>
+        <v>71.68427212098935</v>
       </c>
       <c r="D7" t="n">
-        <v>33.0574086973986</v>
+        <v>33.47661496711198</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.507604620824606</v>
+        <v>5.591053175685585</v>
       </c>
       <c r="C8" t="n">
-        <v>25.95250056176443</v>
+        <v>32.04424506661589</v>
       </c>
       <c r="D8" t="n">
-        <v>32.12769362147687</v>
+        <v>31.2097595180061</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
-        <v>23.07499804061703</v>
+        <v>23.18593553119691</v>
       </c>
       <c r="D9" t="n">
-        <v>31.28437234352885</v>
+        <v>31.39530983410874</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.840016181936776</v>
+        <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.76949457814703</v>
+        <v>24.48478774391545</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>33.31069960509428</v>
       </c>
     </row>
     <row r="11">
@@ -6196,7 +6196,7 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
         <v>35.36157055926586</v>
@@ -6221,10 +6221,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>21.07321447165778</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
         <v>30.95941385342317</v>
@@ -6238,7 +6238,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
         <v>30.11412908006666</v>
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -6283,7 +6283,7 @@
         <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6322,7 +6322,7 @@
         <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.276460916866037</v>
+        <v>7.26125367898406</v>
       </c>
       <c r="C21" t="n">
-        <v>75.49328201248514</v>
+        <v>75.33550691945963</v>
       </c>
       <c r="D21" t="n">
-        <v>5.457345687649528</v>
+        <v>5.445940259238045</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.308890673939251</v>
+        <v>4.564145077043421</v>
       </c>
       <c r="C2" t="n">
-        <v>6.510950774564847</v>
+        <v>11.45405046544754</v>
       </c>
       <c r="D2" t="n">
-        <v>38.24103657582176</v>
+        <v>25.99177046993431</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.79694245613693</v>
+        <v>16.38536918387927</v>
       </c>
       <c r="C3" t="n">
-        <v>31.56809743005618</v>
+        <v>35.10729790386593</v>
       </c>
       <c r="D3" t="n">
-        <v>85.18133955897451</v>
+        <v>64.09339887175302</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.53141291210056</v>
+        <v>29.97962964458485</v>
       </c>
       <c r="C4" t="n">
-        <v>75.19794715448869</v>
+        <v>64.37516046287185</v>
       </c>
       <c r="D4" t="n">
-        <v>90.48768590042852</v>
+        <v>61.80985371167493</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.56381058634071</v>
+        <v>33.84575210390879</v>
       </c>
       <c r="C5" t="n">
-        <v>85.85383673638358</v>
+        <v>109.6857622569749</v>
       </c>
       <c r="D5" t="n">
-        <v>59.49391087735672</v>
+        <v>43.4914232981337</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>27.77364255314227</v>
+        <v>31.27553661419064</v>
       </c>
       <c r="C6" t="n">
-        <v>98.41529861222153</v>
+        <v>149.1726366694859</v>
       </c>
       <c r="D6" t="n">
-        <v>42.18373535607696</v>
+        <v>36.26674194258143</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.34904451882213</v>
+        <v>18.80439552714341</v>
       </c>
       <c r="C7" t="n">
-        <v>76.53508752767283</v>
+        <v>123.3664165156542</v>
       </c>
       <c r="D7" t="n">
-        <v>36.17151241526948</v>
+        <v>35.87207936547421</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.927612711792993</v>
+        <v>8.845546815263761</v>
       </c>
       <c r="C8" t="n">
-        <v>45.72980806381643</v>
+        <v>64.92297568184156</v>
       </c>
       <c r="D8" t="n">
-        <v>33.79666471869644</v>
+        <v>33.46287049925253</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>5.546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>28.28906009787183</v>
+        <v>32.39374724932775</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>32.28280975874785</v>
       </c>
     </row>
     <row r="10">
@@ -6490,10 +6490,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>4.982369599052563</v>
       </c>
       <c r="C10" t="n">
-        <v>26.90479583488384</v>
+        <v>26.76244241776806</v>
       </c>
       <c r="D10" t="n">
         <v>34.02246669067321</v>
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.264712027248144</v>
       </c>
       <c r="C11" t="n">
-        <v>26.65445017030089</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>35.53926689373453</v>
       </c>
     </row>
     <row r="12">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
         <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>31.73990327829938</v>
       </c>
     </row>
     <row r="14">
@@ -6549,10 +6549,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -6563,7 +6563,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D15" t="n">
         <v>29.02537087605695</v>
@@ -6577,10 +6577,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -6622,7 +6622,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6630,10 +6630,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.483063947426261</v>
+        <v>7.463419127891162</v>
       </c>
       <c r="C21" t="n">
-        <v>84.18446940854544</v>
+        <v>83.96346518877557</v>
       </c>
       <c r="D21" t="n">
-        <v>6.547680953997978</v>
+        <v>6.530491736904767</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_31_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_31_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497633841011</v>
+        <v>10.84497644167778</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907196349603</v>
+        <v>37.78907232332985</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.631885668636452</v>
+        <v>1.230129873421253</v>
       </c>
       <c r="C2" t="n">
-        <v>6.752460709809561</v>
+        <v>2.356194490192345</v>
       </c>
       <c r="D2" t="n">
-        <v>20.89551813718911</v>
+        <v>12.67730810493906</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.85031668506475</v>
+        <v>9.979465413668827</v>
       </c>
       <c r="C3" t="n">
-        <v>40.00131020953629</v>
+        <v>32.33876937788994</v>
       </c>
       <c r="D3" t="n">
-        <v>69.1641257641878</v>
+        <v>68.02529842726149</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.78368101436299</v>
+        <v>16.7446888436336</v>
       </c>
       <c r="C4" t="n">
-        <v>75.83608316224911</v>
+        <v>114.9410577178081</v>
       </c>
       <c r="D4" t="n">
-        <v>78.04403374910019</v>
+        <v>82.29401956078463</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.07355862902306</v>
+        <v>15.56070111231195</v>
       </c>
       <c r="C5" t="n">
-        <v>114.2999764669349</v>
+        <v>141.3225820263284</v>
       </c>
       <c r="D5" t="n">
-        <v>54.04521111878692</v>
+        <v>47.39387042251478</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.64158963915446</v>
+        <v>10.38492721552276</v>
       </c>
       <c r="C6" t="n">
-        <v>160.6041069377357</v>
+        <v>89.39892769641881</v>
       </c>
       <c r="D6" t="n">
-        <v>41.45920555034281</v>
+        <v>29.7057220351</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>27.48795397120644</v>
+        <v>5.868887775987432</v>
       </c>
       <c r="C7" t="n">
-        <v>169.658766014004</v>
+        <v>43.41779222031519</v>
       </c>
       <c r="D7" t="n">
-        <v>37.96811071404115</v>
+        <v>28.86534600026472</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.26970288122739</v>
+        <v>6.091744504851458</v>
       </c>
       <c r="C8" t="n">
-        <v>112.4052033977386</v>
+        <v>28.78975142703771</v>
       </c>
       <c r="D8" t="n">
-        <v>35.63253292563798</v>
+        <v>31.04286240828414</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.321874378272709</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>56.13437023342411</v>
+        <v>31.17343485294896</v>
       </c>
       <c r="D9" t="n">
-        <v>33.39218466454675</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.267076433284139</v>
+        <v>3.274128593663113</v>
       </c>
       <c r="C10" t="n">
-        <v>32.88363935374691</v>
+        <v>29.75186417719959</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>37.72365553568369</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>28.96450251839364</v>
+        <v>30.74146586308036</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>37.31623023842126</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>27.55471281509523</v>
+        <v>23.86628669023996</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>37.5351599764683</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>25.23582473766426</v>
+        <v>19.77239876353076</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>35.90251354430586</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.35381438862312</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>27.3485457972034</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
+        <v>24.55547357862122</v>
+      </c>
+      <c r="D17" t="n">
         <v>17.9443845382232</v>
-      </c>
-      <c r="D17" t="n">
-        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>26.75262494072559</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>11.23610247510475</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>10.83260416865931</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>84.85539932116455</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.650059562063402</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>92.75697219001874</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.650059562063402</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.065237316836795</v>
+        <v>0.9984374152190061</v>
       </c>
       <c r="C2" t="n">
-        <v>12.03917209717864</v>
+        <v>4.811545498513618</v>
       </c>
       <c r="D2" t="n">
-        <v>16.55226629360122</v>
+        <v>12.31995194059322</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.5116137270996</v>
+        <v>6.901686360855077</v>
       </c>
       <c r="C3" t="n">
-        <v>32.93272673895925</v>
+        <v>19.03117924682442</v>
       </c>
       <c r="D3" t="n">
-        <v>69.14449081010285</v>
+        <v>62.52751128347936</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.29869764846506</v>
+        <v>18.28897798241383</v>
       </c>
       <c r="C4" t="n">
-        <v>87.23319226085034</v>
+        <v>95.95013012685776</v>
       </c>
       <c r="D4" t="n">
-        <v>90.55149950120456</v>
+        <v>97.03496134005049</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.89608327873264</v>
+        <v>20.56761440397068</v>
       </c>
       <c r="C5" t="n">
-        <v>124.7310458245573</v>
+        <v>181.058820355718</v>
       </c>
       <c r="D5" t="n">
-        <v>67.15154297048184</v>
+        <v>65.08987279156354</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44.71958967614647</v>
+        <v>15.33588088803943</v>
       </c>
       <c r="C6" t="n">
-        <v>170.6670209062655</v>
+        <v>158.994040702771</v>
       </c>
       <c r="D6" t="n">
-        <v>47.2956956520901</v>
+        <v>37.11202671593793</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>35.63253292563798</v>
+        <v>8.803331663981149</v>
       </c>
       <c r="C7" t="n">
-        <v>197.0868333752514</v>
+        <v>85.93728529124455</v>
       </c>
       <c r="D7" t="n">
-        <v>41.02232782195297</v>
+        <v>30.96137734883166</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>21.19593293468863</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>162.2239906497429</v>
+        <v>42.97600575340412</v>
       </c>
       <c r="D8" t="n">
-        <v>37.21805546799658</v>
+        <v>32.3780392860598</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.31718662392973</v>
+        <v>6.101561981893925</v>
       </c>
       <c r="C9" t="n">
-        <v>93.52030455884689</v>
+        <v>34.61249706092553</v>
       </c>
       <c r="D9" t="n">
-        <v>34.94530953266521</v>
+        <v>35.72187196672443</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.121196935978863</v>
+        <v>3.98589567924205</v>
       </c>
       <c r="C10" t="n">
-        <v>47.40368789955724</v>
+        <v>34.02246669067321</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>38.57777603837842</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
         <v>33.40691088011046</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>38.20471191076462</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>29.94134148411922</v>
+        <v>28.42257778564941</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>37.96909246174538</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>27.83745615391831</v>
+        <v>22.63419332141022</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>36.68300296918207</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>25.19753657719863</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>28.88498095434966</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.21695054710532</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.44199175555609</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.25247339090745</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>21.49242074137117</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>16.99994324673777</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>8.560839981032187</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>51.36503988619312</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>9.095892479846698</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>46.33947338815369</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.820799635119276</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>100.6927953021607</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.798399589509186</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.087637587585224</v>
+        <v>0.5409429850399925</v>
       </c>
       <c r="C2" t="n">
-        <v>17.59684585091983</v>
+        <v>2.0469439633546</v>
       </c>
       <c r="D2" t="n">
-        <v>19.64673505738717</v>
+        <v>8.399833357535709</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.19040230136165</v>
+        <v>6.135923151542565</v>
       </c>
       <c r="C3" t="n">
-        <v>38.72503819401544</v>
+        <v>20.19945901487813</v>
       </c>
       <c r="D3" t="n">
-        <v>66.35141859152068</v>
+        <v>60.81436153956867</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.13729011434109</v>
+        <v>19.90984344212531</v>
       </c>
       <c r="C4" t="n">
-        <v>83.91488502049611</v>
+        <v>86.23770008874408</v>
       </c>
       <c r="D4" t="n">
-        <v>100.6468111439745</v>
+        <v>105.6625601649715</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.90237467558562</v>
+        <v>20.44489594093983</v>
       </c>
       <c r="C5" t="n">
-        <v>138.2791641431633</v>
+        <v>205.2098138801896</v>
       </c>
       <c r="D5" t="n">
-        <v>78.83434065101889</v>
+        <v>73.43472827766143</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.26802678992194</v>
+        <v>12.23650338573225</v>
       </c>
       <c r="C6" t="n">
-        <v>182.5010077332566</v>
+        <v>198.6016700829043</v>
       </c>
       <c r="D6" t="n">
-        <v>55.10451689166923</v>
+        <v>37.75605320992383</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>42.63926629084747</v>
+        <v>4.311835917051991</v>
       </c>
       <c r="C7" t="n">
-        <v>216.7895280517806</v>
+        <v>80.24805734513427</v>
       </c>
       <c r="D7" t="n">
-        <v>43.89688509998763</v>
+        <v>32.87774886752143</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>28.37250865273282</v>
+        <v>4.172427743048944</v>
       </c>
       <c r="C8" t="n">
-        <v>202.3627455378738</v>
+        <v>40.22220344299182</v>
       </c>
       <c r="D8" t="n">
-        <v>38.97047512007713</v>
+        <v>36.55046702910875</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14.53281126596553</v>
+        <v>2.773437264497239</v>
       </c>
       <c r="C9" t="n">
-        <v>136.7859258850038</v>
+        <v>25.95937279569415</v>
       </c>
       <c r="D9" t="n">
-        <v>36.38749691020377</v>
+        <v>40.27030908049991</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>1.850594422505238</v>
       </c>
       <c r="C10" t="n">
-        <v>72.88494956328321</v>
+        <v>26.1930287493049</v>
       </c>
       <c r="D10" t="n">
-        <v>35.44600086183109</v>
+        <v>29.89421759431538</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>41.5809422656694</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
-        <v>36.96083756948391</v>
+        <v>30.38607319414302</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>1.301797455831271</v>
       </c>
       <c r="C12" t="n">
-        <v>32.97886888105885</v>
+        <v>18.44213062427633</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>29.94134148411922</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>17.69109363052753</v>
       </c>
       <c r="D13" t="n">
-        <v>33.56104526967722</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>27.04125876577415</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>21.20280516861837</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>24.00864010735575</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>17.91689560250429</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.49242074137117</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>6.611089040398022</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>44.38874069981529</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>7.555530331883453</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>40.12893741108837</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.975603475417684</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>107.6706469181387</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9.969504344272105</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.267878254539137</v>
+        <v>0.988619938176538</v>
       </c>
       <c r="C2" t="n">
-        <v>12.24730261047896</v>
+        <v>7.408268176246431</v>
       </c>
       <c r="D2" t="n">
-        <v>16.35395325734337</v>
+        <v>8.922123136195014</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.238728923048</v>
+        <v>3.951534509593412</v>
       </c>
       <c r="C3" t="n">
-        <v>60.26458282519045</v>
+        <v>13.4204911170539</v>
       </c>
       <c r="D3" t="n">
-        <v>72.40389318820228</v>
+        <v>54.25628687519998</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>20.61179305066178</v>
+        <v>16.01721379478671</v>
       </c>
       <c r="C4" t="n">
-        <v>113.3329549782518</v>
+        <v>67.78280674431252</v>
       </c>
       <c r="D4" t="n">
-        <v>94.03572210357649</v>
+        <v>111.507885996057</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.7343726449724</v>
+        <v>25.30454707696154</v>
       </c>
       <c r="C5" t="n">
-        <v>109.0476262492145</v>
+        <v>183.6359080793659</v>
       </c>
       <c r="D5" t="n">
-        <v>54.11884219660543</v>
+        <v>92.35791527701869</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>26.44533790929634</v>
+        <v>18.75727163733956</v>
       </c>
       <c r="C6" t="n">
-        <v>142.7726233855009</v>
+        <v>262.1187830522645</v>
       </c>
       <c r="D6" t="n">
-        <v>28.90068891761761</v>
+        <v>50.31456984264904</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.80439552714341</v>
+        <v>8.024805734513427</v>
       </c>
       <c r="C7" t="n">
-        <v>142.2905852627157</v>
+        <v>176.6654993792135</v>
       </c>
       <c r="D7" t="n">
-        <v>27.36818075128833</v>
+        <v>36.05173919535137</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.09727513817844</v>
+        <v>4.506221962492859</v>
       </c>
       <c r="C8" t="n">
-        <v>100.8058542720625</v>
+        <v>70.09678608322226</v>
       </c>
       <c r="D8" t="n">
-        <v>26.78698611037422</v>
+        <v>37.21805546799658</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.324999547834698</v>
+        <v>3.217187226816797</v>
       </c>
       <c r="C9" t="n">
-        <v>55.57968278052466</v>
+        <v>36.38749691020377</v>
       </c>
       <c r="D9" t="n">
-        <v>27.06874770149305</v>
+        <v>41.49062147687869</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.558835427894688</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>32.59893251951534</v>
+        <v>29.32480392585223</v>
       </c>
       <c r="D10" t="n">
-        <v>28.89774367450487</v>
+        <v>31.74481201682062</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.843141351498762</v>
+        <v>1.421570675749381</v>
       </c>
       <c r="C11" t="n">
-        <v>26.29905750136355</v>
+        <v>26.12136116689488</v>
       </c>
       <c r="D11" t="n">
-        <v>28.07602084605028</v>
+        <v>31.09685853201771</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.169662426385451</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>21.04572553593887</v>
       </c>
       <c r="D12" t="n">
-        <v>27.33774657245668</v>
+        <v>30.8092064546734</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>22.37403017978481</v>
+        <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
-        <v>24.97566159603886</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>19.97365704290136</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>24.58296251434014</v>
+        <v>20.89551813718911</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>22.21695054710532</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>38.02505208088746</v>
       </c>
       <c r="D16" t="n">
-        <v>20.25247339090745</v>
+        <v>12.39947350463721</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.58328130950962</v>
+        <v>47.22206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>17.47216389248049</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
-        <v>13.37631247036279</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>72.62969516017901</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.216606389740051</v>
+        <v>0.5478152189697202</v>
       </c>
       <c r="C2" t="n">
-        <v>5.60479764354504</v>
+        <v>5.038329218194631</v>
       </c>
       <c r="D2" t="n">
-        <v>11.5119735799981</v>
+        <v>7.199155915241861</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.88944772451438</v>
+        <v>3.769911184307752</v>
       </c>
       <c r="C3" t="n">
-        <v>55.15458602458581</v>
+        <v>21.64262814012093</v>
       </c>
       <c r="D3" t="n">
-        <v>69.54700736884405</v>
+        <v>50.3391135352552</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.12903522207961</v>
+        <v>13.01797455831271</v>
       </c>
       <c r="C4" t="n">
-        <v>134.889189320399</v>
+        <v>53.47579745032376</v>
       </c>
       <c r="D4" t="n">
-        <v>106.5431878556809</v>
+        <v>113.4350567394935</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.65507206510666</v>
+        <v>26.48264432205772</v>
       </c>
       <c r="C5" t="n">
-        <v>154.8707003449344</v>
+        <v>163.608254912731</v>
       </c>
       <c r="D5" t="n">
-        <v>68.10874698212248</v>
+        <v>106.5441696033851</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.99377502307181</v>
+        <v>23.38621206286328</v>
       </c>
       <c r="C6" t="n">
-        <v>161.8921599257075</v>
+        <v>289.328902423169</v>
       </c>
       <c r="D6" t="n">
-        <v>34.5359207399943</v>
+        <v>60.37748381117885</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.42700349808513</v>
+        <v>8.743445054022093</v>
       </c>
       <c r="C7" t="n">
-        <v>172.5932099019978</v>
+        <v>249.3079572595477</v>
       </c>
       <c r="D7" t="n">
-        <v>29.64387192973244</v>
+        <v>39.64493579289469</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.428304040958867</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>129.5956056991002</v>
+        <v>110.9865779651019</v>
       </c>
       <c r="D8" t="n">
-        <v>27.53802310412303</v>
+        <v>39.97185777840888</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.326562132615692</v>
+        <v>2.662499773917349</v>
       </c>
       <c r="C9" t="n">
-        <v>59.57343244140068</v>
+        <v>47.7031209493525</v>
       </c>
       <c r="D9" t="n">
-        <v>28.39999758845172</v>
+        <v>41.49062147687869</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.992947839621025</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>33.88011327355743</v>
+        <v>31.60245859970483</v>
       </c>
       <c r="D10" t="n">
-        <v>29.60951076008381</v>
+        <v>32.59893251951534</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>27.00984283923824</v>
       </c>
       <c r="D11" t="n">
-        <v>29.31989518733098</v>
+        <v>32.51842920776709</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>20.39482680802324</v>
+        <v>22.99842171968578</v>
       </c>
       <c r="D12" t="n">
-        <v>28.20561154301086</v>
+        <v>29.50740899884213</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>16.3902779224005</v>
+        <v>17.69109363052753</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>24.19517217116264</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>18.4372218857551</v>
+        <v>16.59349969717959</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>32.25041208450772</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.22610507161303</v>
+        <v>40.5049467818149</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>11.33329549782518</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>63.19019098384595</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.791509633801182</v>
+        <v>0.5085453107998478</v>
       </c>
       <c r="C2" t="n">
-        <v>10.19937689942011</v>
+        <v>8.932922360941728</v>
       </c>
       <c r="D2" t="n">
-        <v>15.48510653908494</v>
+        <v>8.354672963140356</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.61393647251952</v>
+        <v>2.82252464970958</v>
       </c>
       <c r="C3" t="n">
-        <v>38.20962064928586</v>
+        <v>20.67069791291659</v>
       </c>
       <c r="D3" t="n">
-        <v>63.23927836905829</v>
+        <v>45.00331476267379</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.37826027023806</v>
+        <v>10.21017612416683</v>
       </c>
       <c r="C4" t="n">
-        <v>136.0761222948334</v>
+        <v>53.66723825265188</v>
       </c>
       <c r="D4" t="n">
-        <v>115.426041083706</v>
+        <v>112.8224461720434</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.7356164345839</v>
+        <v>24.00373136883452</v>
       </c>
       <c r="C5" t="n">
-        <v>198.8039101099791</v>
+        <v>132.7813769993811</v>
       </c>
       <c r="D5" t="n">
-        <v>87.03193398147975</v>
+        <v>120.4358996184775</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.54221213684728</v>
+        <v>28.73968229412113</v>
       </c>
       <c r="C6" t="n">
-        <v>201.7412992410856</v>
+        <v>280.3527831632405</v>
       </c>
       <c r="D6" t="n">
-        <v>45.16235789076178</v>
+        <v>76.03537794621123</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.91282974296706</v>
+        <v>15.9897248590678</v>
       </c>
       <c r="C7" t="n">
-        <v>200.6201433628357</v>
+        <v>323.7470134386537</v>
       </c>
       <c r="D7" t="n">
-        <v>32.27888276793088</v>
+        <v>46.11268966847268</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.01659189998096</v>
+        <v>6.175193059712437</v>
       </c>
       <c r="C8" t="n">
-        <v>174.2405825497239</v>
+        <v>204.6993050739812</v>
       </c>
       <c r="D8" t="n">
-        <v>29.2069942013426</v>
+        <v>41.47393176590651</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>3.217187226816797</v>
       </c>
       <c r="C9" t="n">
-        <v>101.5078038805989</v>
+        <v>84.31249284071605</v>
       </c>
       <c r="D9" t="n">
-        <v>28.95468504135117</v>
+        <v>42.82187136383736</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.420008090968388</v>
+        <v>1.565887588273662</v>
       </c>
       <c r="C10" t="n">
-        <v>47.83074815090461</v>
+        <v>41.70955121492574</v>
       </c>
       <c r="D10" t="n">
-        <v>30.17892442854695</v>
+        <v>34.16482010778901</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>33.40691088011046</v>
+        <v>31.27455486648638</v>
       </c>
       <c r="D11" t="n">
-        <v>29.49759152179966</v>
+        <v>33.05151821117311</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>26.25291535926396</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>30.15830772675777</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.47158305540374</v>
+        <v>20.03256190515617</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>24.71549845441346</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>15.97892563432109</v>
+        <v>20.58823110575986</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>16.90078672860884</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.5083653843506</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>33.32542582065798</v>
       </c>
       <c r="D15" t="n">
-        <v>16.84188186635403</v>
+        <v>10.0334615374024</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.05273663858884</v>
+        <v>40.5049467818149</v>
       </c>
       <c r="D16" t="n">
-        <v>14.46605242207675</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>10.38885420633975</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>33.09962384868121</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.295326132529043</v>
+        <v>0.3455751918948772</v>
       </c>
       <c r="C2" t="n">
-        <v>4.916592502868026</v>
+        <v>4.716315971201677</v>
       </c>
       <c r="D2" t="n">
-        <v>10.80020649441916</v>
+        <v>6.082908775513236</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.04943154257761</v>
+        <v>3.809181092477624</v>
       </c>
       <c r="C3" t="n">
-        <v>41.25794727097221</v>
+        <v>28.81429511964389</v>
       </c>
       <c r="D3" t="n">
-        <v>63.29327449279187</v>
+        <v>48.29216957190061</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.86248287260999</v>
+        <v>16.55324804130547</v>
       </c>
       <c r="C4" t="n">
-        <v>135.0168165219511</v>
+        <v>78.32481359251477</v>
       </c>
       <c r="D4" t="n">
-        <v>122.5476389303124</v>
+        <v>116.7150758193821</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.35550014659114</v>
+        <v>17.72054606165493</v>
       </c>
       <c r="C5" t="n">
-        <v>244.9951395947916</v>
+        <v>219.0770002026758</v>
       </c>
       <c r="D5" t="n">
-        <v>91.49888603580274</v>
+        <v>111.281102276376</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.26295382048468</v>
+        <v>9.901907345033331</v>
       </c>
       <c r="C6" t="n">
-        <v>236.1967166693317</v>
+        <v>279.185485142891</v>
       </c>
       <c r="D6" t="n">
-        <v>44.23656980565704</v>
+        <v>64.12088780747193</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.964919124554372</v>
+        <v>4.07228947721577</v>
       </c>
       <c r="C7" t="n">
-        <v>216.7296414418216</v>
+        <v>143.9075237316102</v>
       </c>
       <c r="D7" t="n">
-        <v>32.75797564760332</v>
+        <v>35.45287309576081</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.922082078466008</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C8" t="n">
-        <v>124.3383467428585</v>
+        <v>62.08572481656828</v>
       </c>
       <c r="D8" t="n">
-        <v>30.95941385342316</v>
+        <v>31.54355373745002</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.664062358698343</v>
+        <v>1.109374905798895</v>
       </c>
       <c r="C9" t="n">
-        <v>36.49843440078366</v>
+        <v>31.8390597964283</v>
       </c>
       <c r="D9" t="n">
-        <v>31.50624732468863</v>
+        <v>26.07031028627404</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>26.1930287493049</v>
+        <v>24.48478774391545</v>
       </c>
       <c r="D10" t="n">
-        <v>23.06125357275758</v>
+        <v>25.90832191507333</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>19.72429312602266</v>
+        <v>20.96816746730337</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>14.97067074205961</v>
+        <v>16.27246819789088</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>20.17786056538469</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>13.00815708127024</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>13.78864650614645</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>8.296749848589794</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>11.82515109765283</v>
+        <v>34.40043955680824</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.679631453246051</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>28.35778243716912</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.418044595559894</v>
+        <v>0.2513274122871835</v>
       </c>
       <c r="C2" t="n">
-        <v>7.932521450314227</v>
+        <v>3.065016332658542</v>
       </c>
       <c r="D2" t="n">
-        <v>10.66767055434584</v>
+        <v>5.21406205725481</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.26832022289564</v>
+        <v>2.513274122871834</v>
       </c>
       <c r="C3" t="n">
-        <v>30.42927009312989</v>
+        <v>23.1937895128309</v>
       </c>
       <c r="D3" t="n">
-        <v>57.94765824316799</v>
+        <v>42.25442119078272</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.64176956560371</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C4" t="n">
-        <v>119.6887896155456</v>
+        <v>71.98174167537614</v>
       </c>
       <c r="D4" t="n">
-        <v>125.2660983233718</v>
+        <v>110.0529358983632</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.79853040311371</v>
+        <v>16.73879835740812</v>
       </c>
       <c r="C5" t="n">
-        <v>248.5785187152924</v>
+        <v>165.9399057103171</v>
       </c>
       <c r="D5" t="n">
-        <v>109.4648690235194</v>
+        <v>114.8399377042707</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.23278168356029</v>
+        <v>9.94215900090745</v>
       </c>
       <c r="C6" t="n">
-        <v>303.1754720438661</v>
+        <v>260.1464519144326</v>
       </c>
       <c r="D6" t="n">
-        <v>58.28439770572465</v>
+        <v>67.90454345963914</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.92983824910874</v>
+        <v>3.413536767666159</v>
       </c>
       <c r="C7" t="n">
-        <v>272.3643020937841</v>
+        <v>185.2292846033585</v>
       </c>
       <c r="D7" t="n">
-        <v>36.29128563518759</v>
+        <v>34.37491411649782</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.17381040138069</v>
+        <v>1.084831213192726</v>
       </c>
       <c r="C8" t="n">
-        <v>187.5923513274805</v>
+        <v>73.26783116793945</v>
       </c>
       <c r="D8" t="n">
-        <v>32.46148784092078</v>
+        <v>27.12078032981814</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>76.65780599070366</v>
+        <v>30.17499743772996</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>20.63437324785945</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>32.45657910239955</v>
+        <v>17.79417713947344</v>
       </c>
       <c r="D10" t="n">
-        <v>24.34243432679967</v>
+        <v>19.78712497909446</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.92282714645877</v>
+        <v>13.50492141961912</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>17.59193711239859</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.14033316844506</v>
+        <v>11.49921085984289</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>14.82929907264807</v>
+        <v>14.56913593102267</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>8.065057390387548</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.82791641431633</v>
+        <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>13.82791641431633</v>
+        <v>2.765583282863265</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.90016483380309</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>11.46681318560274</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.97231544229862</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>7.852999886270235</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.0554452019901</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.645409152317654</v>
+        <v>0.1806415775814131</v>
       </c>
       <c r="C2" t="n">
-        <v>4.130212591766331</v>
+        <v>9.61523701539326</v>
       </c>
       <c r="D2" t="n">
-        <v>7.595781987757572</v>
+        <v>9.842020735074273</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.32936850700819</v>
+        <v>1.614974973486003</v>
       </c>
       <c r="C3" t="n">
-        <v>30.85142160595602</v>
+        <v>16.45900026169778</v>
       </c>
       <c r="D3" t="n">
-        <v>54.36918786118836</v>
+        <v>37.02661466566845</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.1958351236974</v>
+        <v>7.900123776074084</v>
       </c>
       <c r="C4" t="n">
-        <v>105.0627123176767</v>
+        <v>64.66870302644165</v>
       </c>
       <c r="D4" t="n">
-        <v>125.8276580102009</v>
+        <v>105.6115092843506</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.65189014228245</v>
+        <v>17.27875959474386</v>
       </c>
       <c r="C5" t="n">
-        <v>244.3815472796373</v>
+        <v>147.9493790299944</v>
       </c>
       <c r="D5" t="n">
-        <v>122.1048707156971</v>
+        <v>129.0016483380309</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.98876847355934</v>
+        <v>16.22141731727005</v>
       </c>
       <c r="C6" t="n">
-        <v>346.1642405174254</v>
+        <v>265.9024387044316</v>
       </c>
       <c r="D6" t="n">
-        <v>68.0252984272615</v>
+        <v>87.74860980557993</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>14.19312656029614</v>
+        <v>7.306166415004762</v>
       </c>
       <c r="C7" t="n">
-        <v>331.1729530735765</v>
+        <v>284.0421910357999</v>
       </c>
       <c r="D7" t="n">
-        <v>40.12402867256714</v>
+        <v>45.09461729916874</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.172427743048944</v>
+        <v>2.253110981246429</v>
       </c>
       <c r="C8" t="n">
-        <v>234.3235420496287</v>
+        <v>160.8888137719673</v>
       </c>
       <c r="D8" t="n">
-        <v>33.71321616383547</v>
+        <v>30.29182541453534</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.553124868118454</v>
+        <v>0.6656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>83.09218044433726</v>
+        <v>60.01718240372024</v>
       </c>
       <c r="D9" t="n">
-        <v>31.94999728700819</v>
+        <v>22.52031058771757</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>32.31422568528377</v>
+        <v>26.62008900065227</v>
       </c>
       <c r="D10" t="n">
-        <v>24.91184799526281</v>
+        <v>20.35653864755762</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.38973814305275</v>
+        <v>16.8811517745239</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>18.30272245027328</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.27246819789088</v>
+        <v>13.23494080095125</v>
       </c>
       <c r="D12" t="n">
-        <v>19.7439280801076</v>
+        <v>14.10280577150543</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>11.44717823151781</v>
+        <v>14.56913593102267</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>8.585383673638358</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>10.75504610002381</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>3.072870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.10547327717769</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.190279128174634</v>
+        <v>0.212057504117311</v>
       </c>
       <c r="C2" t="n">
-        <v>9.804714322312895</v>
+        <v>6.935065782799468</v>
       </c>
       <c r="D2" t="n">
-        <v>15.02270337038469</v>
+        <v>8.334056261351174</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>8.673740967020569</v>
+        <v>1.084831213192726</v>
       </c>
       <c r="C3" t="n">
-        <v>24.1166323548229</v>
+        <v>27.8080037227909</v>
       </c>
       <c r="D3" t="n">
-        <v>49.13647259755286</v>
+        <v>36.23139902522853</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.03969618099315</v>
+        <v>5.475206946584461</v>
       </c>
       <c r="C4" t="n">
-        <v>92.84878912914209</v>
+        <v>52.1867627146477</v>
       </c>
       <c r="D4" t="n">
-        <v>124.0791653489374</v>
+        <v>100.7744383455266</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.43099690882691</v>
+        <v>14.99619618237003</v>
       </c>
       <c r="C5" t="n">
-        <v>223.0285347122692</v>
+        <v>133.3213382367169</v>
       </c>
       <c r="D5" t="n">
-        <v>132.1677846842269</v>
+        <v>135.9229696529709</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>51.20010627187966</v>
+        <v>19.60255641069606</v>
       </c>
       <c r="C6" t="n">
-        <v>363.3114459198002</v>
+        <v>252.2168757072311</v>
       </c>
       <c r="D6" t="n">
-        <v>83.64294090641977</v>
+        <v>106.7473913781642</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.45180923259856</v>
+        <v>12.93550775115597</v>
       </c>
       <c r="C7" t="n">
-        <v>399.1442553771044</v>
+        <v>335.3051291607513</v>
       </c>
       <c r="D7" t="n">
-        <v>46.8912155979404</v>
+        <v>58.03012505032471</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.260024272905162</v>
+        <v>4.756567627075796</v>
       </c>
       <c r="C8" t="n">
-        <v>307.6748217724291</v>
+        <v>264.3650217995811</v>
       </c>
       <c r="D8" t="n">
-        <v>35.71598148049896</v>
+        <v>34.46425315758427</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.218749811597791</v>
+        <v>1.331249886958674</v>
       </c>
       <c r="C9" t="n">
-        <v>153.2046744908274</v>
+        <v>124.8046769023757</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>24.84999788989526</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>52.95547116707295</v>
+        <v>46.83427423109409</v>
       </c>
       <c r="D10" t="n">
-        <v>26.1930287493049</v>
+        <v>21.21065915025234</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>23.10052348092744</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>19.01350778814797</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.87606310955342</v>
+        <v>15.83853571261379</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>14.75370449942107</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.00815708127024</v>
+        <v>14.82929907264807</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>9.365873098514571</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>3.68744437715102</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>8.241771977151972</v>
       </c>
       <c r="D15" t="n">
-        <v>6.091744504851459</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>26.45221014322606</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.533130061135023</v>
+        <v>3.792491381505428</v>
       </c>
       <c r="C2" t="n">
-        <v>13.8799490426414</v>
+        <v>8.508807352707105</v>
       </c>
       <c r="D2" t="n">
-        <v>7.119634351197869</v>
+        <v>5.225843029705771</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.61890196430299</v>
+        <v>0.3269219855141878</v>
       </c>
       <c r="C2" t="n">
-        <v>5.805074175211389</v>
+        <v>7.025386571590175</v>
       </c>
       <c r="D2" t="n">
-        <v>11.17621586514569</v>
+        <v>12.18447075740716</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.76624623539802</v>
+        <v>0.8933904108645975</v>
       </c>
       <c r="C3" t="n">
-        <v>32.18168974521045</v>
+        <v>27.19441140763665</v>
       </c>
       <c r="D3" t="n">
-        <v>55.04168503859743</v>
+        <v>34.54770171244526</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.08395694314227</v>
+        <v>3.841578766717769</v>
       </c>
       <c r="C4" t="n">
-        <v>131.1241868746125</v>
+        <v>60.36766633413637</v>
       </c>
       <c r="D4" t="n">
-        <v>126.7338111412208</v>
+        <v>95.73316388421922</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.83883881225006</v>
+        <v>12.12458414744811</v>
       </c>
       <c r="C5" t="n">
-        <v>319.3625281914875</v>
+        <v>114.6926755486336</v>
       </c>
       <c r="D5" t="n">
-        <v>119.3805208364122</v>
+        <v>140.6599023259618</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>15.77864910265474</v>
+        <v>20.16607959293373</v>
       </c>
       <c r="C6" t="n">
-        <v>323.4220549485481</v>
+        <v>235.311180240101</v>
       </c>
       <c r="D6" t="n">
-        <v>67.34102027740147</v>
+        <v>120.9964775576024</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4.790928796724434</v>
+        <v>17.30723027816702</v>
       </c>
       <c r="C7" t="n">
-        <v>216.3703217820673</v>
+        <v>351.9536067293688</v>
       </c>
       <c r="D7" t="n">
-        <v>30.60205768907732</v>
+        <v>72.22325161062085</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.50207398749762</v>
+        <v>8.595201150680824</v>
       </c>
       <c r="C8" t="n">
-        <v>112.9058947269044</v>
+        <v>343.1404575883452</v>
       </c>
       <c r="D8" t="n">
-        <v>24.20008090968387</v>
+        <v>40.47254910757476</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3328124717396686</v>
+        <v>2.662499773917349</v>
       </c>
       <c r="C9" t="n">
-        <v>40.38124657107979</v>
+        <v>213.5546693662874</v>
       </c>
       <c r="D9" t="n">
-        <v>19.96874830438012</v>
+        <v>26.95781021091316</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>20.92595231602077</v>
+        <v>88.97088569736719</v>
       </c>
       <c r="D10" t="n">
-        <v>18.93300447639974</v>
+        <v>22.34948648717864</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.10418842983717</v>
+        <v>35.18387422479719</v>
       </c>
       <c r="D11" t="n">
-        <v>16.17036643664921</v>
+        <v>19.36890045708532</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.63134588928871</v>
+        <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
-        <v>12.80100831567416</v>
+        <v>15.4046032273367</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.365873098514571</v>
+        <v>16.1301147807751</v>
       </c>
       <c r="D13" t="n">
-        <v>8.845546815263763</v>
+        <v>10.14636252339079</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>4.916592502868027</v>
+        <v>4.302018440009523</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.21695054710532</v>
+        <v>11.46681318560274</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>0.3583379120500857</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.15301377314226</v>
+        <v>4.025165587411922</v>
       </c>
       <c r="C2" t="n">
-        <v>8.995754214013523</v>
+        <v>14.22748772994478</v>
       </c>
       <c r="D2" t="n">
-        <v>11.97241325328985</v>
+        <v>17.80693985962865</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.75642875835555</v>
+        <v>6.268459091615885</v>
       </c>
       <c r="C3" t="n">
-        <v>34.97476196379262</v>
+        <v>16.79770321966292</v>
       </c>
       <c r="D3" t="n">
-        <v>9.115527433931634</v>
+        <v>6.631705742187204</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>3.632466505713199</v>
       </c>
       <c r="C5" t="n">
-        <v>9.35114688295087</v>
+        <v>8.197593330460869</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>14.49059611468292</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.49536598448391</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39744738623795</v>
+        <v>11.67868273698047</v>
       </c>
       <c r="C21" t="n">
-        <v>70.13957749265748</v>
+        <v>59.9505713831664</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576170280733876</v>
+        <v>0.7785788491320311</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.802709769175396</v>
+        <v>3.704134088123216</v>
       </c>
       <c r="C2" t="n">
-        <v>9.353110378359363</v>
+        <v>6.33718143091316</v>
       </c>
       <c r="D2" t="n">
-        <v>15.02957560431442</v>
+        <v>29.14612584367931</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.49750940634166</v>
+        <v>11.14774518172253</v>
       </c>
       <c r="C3" t="n">
-        <v>35.0434843030899</v>
+        <v>42.63239405691775</v>
       </c>
       <c r="D3" t="n">
-        <v>16.96950906790612</v>
+        <v>20.63142800474672</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>13.71992416684918</v>
+        <v>7.861835615608458</v>
       </c>
       <c r="C4" t="n">
-        <v>53.8331536146696</v>
+        <v>27.84825537866502</v>
       </c>
       <c r="D4" t="n">
-        <v>19.84602984134927</v>
+        <v>17.62531653434299</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>2.454369260617026</v>
       </c>
       <c r="C5" t="n">
-        <v>5.473243451175969</v>
+        <v>5.056000676871074</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>25.72178985126644</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>5.433973543006096</v>
       </c>
       <c r="C6" t="n">
-        <v>16.34217228489241</v>
+        <v>13.68556299720054</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>30.06798693796707</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>6.827073535332318</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.58292145661112</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>20.36144738607885</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>20.85624822901923</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>22.776546738526</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>24.6997904911455</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>28.8565102709265</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.57268737340794</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>40.32528695193774</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43764170860733</v>
+        <v>13.62976071826539</v>
       </c>
       <c r="C21" t="n">
-        <v>86.12579058486195</v>
+        <v>73.76105800473032</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250029833391017</v>
+        <v>1.603501260972398</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.960370238931633</v>
+        <v>1.983130362578557</v>
       </c>
       <c r="C2" t="n">
-        <v>7.117670855789376</v>
+        <v>7.547676350249478</v>
       </c>
       <c r="D2" t="n">
-        <v>16.69265621530852</v>
+        <v>26.03005863039993</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.04943154257761</v>
+        <v>12.26202882604266</v>
       </c>
       <c r="C3" t="n">
-        <v>35.82397372796611</v>
+        <v>31.26375564173968</v>
       </c>
       <c r="D3" t="n">
-        <v>25.0542014123786</v>
+        <v>40.12893741108837</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.9165768073348</v>
+        <v>16.18312915680442</v>
       </c>
       <c r="C4" t="n">
-        <v>73.46221721338033</v>
+        <v>76.66565997233766</v>
       </c>
       <c r="D4" t="n">
-        <v>23.89181213055038</v>
+        <v>24.33850733598268</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>12.10004045484194</v>
+        <v>7.608544707912782</v>
       </c>
       <c r="C5" t="n">
-        <v>57.99674562838034</v>
+        <v>32.86400439966199</v>
       </c>
       <c r="D5" t="n">
-        <v>29.82058651649687</v>
+        <v>26.26175108860219</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.916993413495527</v>
+        <v>4.467933802027235</v>
       </c>
       <c r="C6" t="n">
-        <v>12.23650338573225</v>
+        <v>10.50568218314512</v>
       </c>
       <c r="D6" t="n">
-        <v>36.54850353370026</v>
+        <v>31.95981476405067</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>6.886960145291375</v>
       </c>
       <c r="C7" t="n">
-        <v>24.37385025333556</v>
+        <v>20.00212772632452</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>32.81786225756237</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>7.593818492349078</v>
       </c>
       <c r="C8" t="n">
-        <v>29.54078842078653</v>
+        <v>23.94973524510094</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>33.96356182841841</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>23.96249796525614</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>36.49843440078366</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>24.62714116103124</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.69897297435728</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>6.219371706403542</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.95717262057418</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>31.46010518258904</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>41.44055234396211</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72464595942436</v>
+        <v>14.83756829345786</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0203403524886</v>
+        <v>87.37679106147405</v>
       </c>
       <c r="D21" t="n">
-        <v>4.18116148985609</v>
+        <v>2.472928048909643</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.687845287778519</v>
+        <v>1.604175748739288</v>
       </c>
       <c r="C2" t="n">
-        <v>4.487568756112171</v>
+        <v>5.415320336625406</v>
       </c>
       <c r="D2" t="n">
-        <v>24.72727942686441</v>
+        <v>25.35559795758237</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.59015354343935</v>
+        <v>9.213702204356315</v>
       </c>
       <c r="C3" t="n">
-        <v>31.13121970166636</v>
+        <v>30.11511082777091</v>
       </c>
       <c r="D3" t="n">
-        <v>32.16696352964674</v>
+        <v>51.63992924338223</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.23037621979529</v>
+        <v>20.61179305066178</v>
       </c>
       <c r="C4" t="n">
-        <v>82.31954500109505</v>
+        <v>77.68667758475436</v>
       </c>
       <c r="D4" t="n">
-        <v>30.68157925312132</v>
+        <v>38.95182191369645</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>25.77087723647878</v>
+        <v>16.24792450528471</v>
       </c>
       <c r="C5" t="n">
-        <v>98.59201319898595</v>
+        <v>94.86137192284806</v>
       </c>
       <c r="D5" t="n">
-        <v>31.39138284329177</v>
+        <v>28.93701358267474</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.10945702125691</v>
+        <v>7.607562960208536</v>
       </c>
       <c r="C6" t="n">
-        <v>53.45419900083034</v>
+        <v>33.2881194078966</v>
       </c>
       <c r="D6" t="n">
-        <v>38.15856976866503</v>
+        <v>33.52962934314132</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.563785224144926</v>
+        <v>6.347980655659875</v>
       </c>
       <c r="C7" t="n">
-        <v>21.31963314542373</v>
+        <v>17.66654993792135</v>
       </c>
       <c r="D7" t="n">
-        <v>39.88448223273092</v>
+        <v>35.03366682604743</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.6814150222053</v>
+        <v>7.844164156932015</v>
       </c>
       <c r="C8" t="n">
-        <v>31.29320807286708</v>
+        <v>25.86905200690345</v>
       </c>
       <c r="D8" t="n">
-        <v>39.30426933952106</v>
+        <v>35.21529015133309</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>7.987499321752047</v>
       </c>
       <c r="C9" t="n">
-        <v>34.05780960802609</v>
+        <v>27.73437264497238</v>
       </c>
       <c r="D9" t="n">
-        <v>42.15624642035802</v>
+        <v>37.49687181600267</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
-        <v>33.45305302221006</v>
+        <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
-        <v>48.68486865359933</v>
+        <v>44.55661955724149</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>6.574764375340887</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>27.8983245115816</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>45.4902616239802</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.159886007071988</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>34.28066633689012</v>
+        <v>29.07347651356504</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>42.95931604243193</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>32.5203927031756</v>
+        <v>28.09761929554372</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>41.62610266006477</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>25.27607639353838</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.67733346713483</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.03915952918638</v>
+        <v>16.0745288333194</v>
       </c>
       <c r="C21" t="n">
-        <v>117.6840407380254</v>
+        <v>100.6773121665794</v>
       </c>
       <c r="D21" t="n">
-        <v>6.013053176395459</v>
+        <v>3.3841113333304</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.488951414443917</v>
+        <v>2.565306751196915</v>
       </c>
       <c r="C2" t="n">
-        <v>7.667449570167589</v>
+        <v>9.072330534944774</v>
       </c>
       <c r="D2" t="n">
-        <v>26.76538766088079</v>
+        <v>23.02002016917921</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.02917469368692</v>
+        <v>7.186393195086652</v>
       </c>
       <c r="C3" t="n">
-        <v>22.21695054710532</v>
+        <v>24.92166547230528</v>
       </c>
       <c r="D3" t="n">
-        <v>40.51181901574463</v>
+        <v>59.42518853805944</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.04121770804514</v>
+        <v>19.22065655374405</v>
       </c>
       <c r="C4" t="n">
-        <v>66.03431408304895</v>
+        <v>75.64464235992098</v>
       </c>
       <c r="D4" t="n">
-        <v>33.61700488881928</v>
+        <v>55.14771379065608</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>22.23658550119026</v>
+        <v>23.41468274628643</v>
       </c>
       <c r="C5" t="n">
-        <v>94.05143006684445</v>
+        <v>121.1476667040564</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>35.71107274197773</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.31700669748049</v>
+        <v>14.73210604992764</v>
       </c>
       <c r="C6" t="n">
-        <v>70.88316599432396</v>
+        <v>93.94736481019429</v>
       </c>
       <c r="D6" t="n">
-        <v>30.3497485290859</v>
+        <v>35.46170882509904</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.449681506274044</v>
+        <v>7.785259294677205</v>
       </c>
       <c r="C7" t="n">
-        <v>31.38058361854505</v>
+        <v>33.23706852727577</v>
       </c>
       <c r="D7" t="n">
-        <v>31.26081039862693</v>
+        <v>37.12969817461437</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.756567627075796</v>
+        <v>7.760715602071035</v>
       </c>
       <c r="C8" t="n">
-        <v>18.44213062427633</v>
+        <v>25.20146356801562</v>
       </c>
       <c r="D8" t="n">
-        <v>29.37389131106456</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.77031209493525</v>
+        <v>8.209374302911826</v>
       </c>
       <c r="C9" t="n">
-        <v>21.85468564423824</v>
+        <v>30.39687241888974</v>
       </c>
       <c r="D9" t="n">
-        <v>30.17499743772996</v>
+        <v>38.49530923122167</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>7.971791358484101</v>
       </c>
       <c r="C10" t="n">
-        <v>21.21065915025234</v>
+        <v>30.89069151412589</v>
       </c>
       <c r="D10" t="n">
-        <v>33.16834618797849</v>
+        <v>44.55661955724149</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>6.930157044278233</v>
       </c>
       <c r="C11" t="n">
-        <v>20.43507846389736</v>
+        <v>30.38607319414302</v>
       </c>
       <c r="D11" t="n">
-        <v>34.65078522139116</v>
+        <v>45.84565429291754</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.820561154301086</v>
+        <v>5.858088551240717</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>31.02617269731195</v>
       </c>
       <c r="D12" t="n">
-        <v>31.89403766786613</v>
+        <v>44.04414725562465</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>30.43908757017236</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>41.88626580169016</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>28.5776939229204</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>23.13881164139307</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.044646155996231</v>
+        <v>17.33413746110906</v>
       </c>
       <c r="C21" t="n">
-        <v>66.04355771246466</v>
+        <v>114.4053072433198</v>
       </c>
       <c r="D21" t="n">
-        <v>4.402903847497645</v>
+        <v>4.333534365277266</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.578871292607124</v>
+        <v>2.724349879284899</v>
       </c>
       <c r="C2" t="n">
-        <v>10.48997421987717</v>
+        <v>8.401796852944203</v>
       </c>
       <c r="D2" t="n">
-        <v>29.89716283742811</v>
+        <v>22.82465237603409</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.15113239319178</v>
+        <v>7.898160280665589</v>
       </c>
       <c r="C3" t="n">
-        <v>27.1158715912969</v>
+        <v>30.35073027679015</v>
       </c>
       <c r="D3" t="n">
-        <v>53.20581683165589</v>
+        <v>63.35217935504667</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.53820303057228</v>
+        <v>16.33628179866692</v>
       </c>
       <c r="C4" t="n">
-        <v>59.72953032637594</v>
+        <v>68.6506717148667</v>
       </c>
       <c r="D4" t="n">
-        <v>47.04338649209866</v>
+        <v>70.62889333892403</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.74066404182538</v>
+        <v>26.18812001078367</v>
       </c>
       <c r="C5" t="n">
-        <v>111.0602090429204</v>
+        <v>130.3024640461579</v>
       </c>
       <c r="D5" t="n">
-        <v>34.28753857081986</v>
+        <v>46.09305471438775</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>22.1786623866397</v>
+        <v>22.46042397775853</v>
       </c>
       <c r="C6" t="n">
-        <v>116.448040443827</v>
+        <v>140.3172723771796</v>
       </c>
       <c r="D6" t="n">
-        <v>33.04660947265189</v>
+        <v>38.15856976866503</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.71970318267092</v>
+        <v>12.39652826152447</v>
       </c>
       <c r="C7" t="n">
-        <v>71.68427212098935</v>
+        <v>82.28420208374216</v>
       </c>
       <c r="D7" t="n">
-        <v>33.47661496711198</v>
+        <v>39.16584291322225</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.591053175685585</v>
+        <v>8.261406931236909</v>
       </c>
       <c r="C8" t="n">
-        <v>32.04424506661589</v>
+        <v>34.46425315758427</v>
       </c>
       <c r="D8" t="n">
-        <v>31.2097595180061</v>
+        <v>38.05254101660637</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>8.431249284071605</v>
       </c>
       <c r="C9" t="n">
-        <v>23.18593553119691</v>
+        <v>31.39530983410874</v>
       </c>
       <c r="D9" t="n">
-        <v>31.39530983410874</v>
+        <v>39.49374664644068</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>8.114144775599888</v>
       </c>
       <c r="C10" t="n">
-        <v>24.48478774391545</v>
+        <v>34.16482010778901</v>
       </c>
       <c r="D10" t="n">
-        <v>33.31069960509428</v>
+        <v>44.69897297435728</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.285549713215578</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>33.40691088011046</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>46.02335062738621</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>32.76190263842031</v>
       </c>
       <c r="D12" t="n">
-        <v>33.1958351236974</v>
+        <v>44.91201222617883</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>20.81305133003238</v>
+        <v>32.780555844801</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>42.14642894331557</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>31.03599017435442</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>42.09832330580748</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>28.66703296400686</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.43836786437537</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>24.07245370813179</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.26125367898406</v>
+        <v>17.72366669416338</v>
       </c>
       <c r="C21" t="n">
-        <v>75.33550691945963</v>
+        <v>127.6104001979763</v>
       </c>
       <c r="D21" t="n">
-        <v>5.445940259238045</v>
+        <v>5.317100008249014</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.564145077043421</v>
+        <v>2.448478774391545</v>
       </c>
       <c r="C2" t="n">
-        <v>11.45405046544754</v>
+        <v>5.242532740677968</v>
       </c>
       <c r="D2" t="n">
-        <v>25.99177046993431</v>
+        <v>18.13778883595982</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.38536918387927</v>
+        <v>10.73541114593887</v>
       </c>
       <c r="C3" t="n">
-        <v>35.10729790386593</v>
+        <v>45.65126824747668</v>
       </c>
       <c r="D3" t="n">
-        <v>64.09339887175302</v>
+        <v>68.98741117742337</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.97962964458485</v>
+        <v>12.57127935288041</v>
       </c>
       <c r="C4" t="n">
-        <v>64.37516046287185</v>
+        <v>107.2196120239069</v>
       </c>
       <c r="D4" t="n">
-        <v>61.80985371167493</v>
+        <v>64.23477054116456</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.84575210390879</v>
+        <v>12.64000169217769</v>
       </c>
       <c r="C5" t="n">
-        <v>109.6857622569749</v>
+        <v>83.84125394267762</v>
       </c>
       <c r="D5" t="n">
-        <v>43.4914232981337</v>
+        <v>36.05468443846411</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.27553661419064</v>
+        <v>7.688066271956774</v>
       </c>
       <c r="C6" t="n">
-        <v>149.1726366694859</v>
+        <v>54.17872880656449</v>
       </c>
       <c r="D6" t="n">
-        <v>36.26674194258143</v>
+        <v>25.76105975943631</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.80439552714341</v>
+        <v>5.449681506274044</v>
       </c>
       <c r="C7" t="n">
-        <v>123.3664165156542</v>
+        <v>24.19419042345839</v>
       </c>
       <c r="D7" t="n">
-        <v>35.87207936547421</v>
+        <v>26.70942804173872</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.845546815263761</v>
+        <v>5.841398840268521</v>
       </c>
       <c r="C8" t="n">
-        <v>64.92297568184156</v>
+        <v>23.11524969649115</v>
       </c>
       <c r="D8" t="n">
-        <v>33.46287049925253</v>
+        <v>29.04009709162065</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.546874528994477</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>32.39374724932775</v>
+        <v>26.07031028627404</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>34.05780960802609</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.267076433284139</v>
       </c>
       <c r="C10" t="n">
-        <v>26.76244241776806</v>
+        <v>26.1930287493049</v>
       </c>
       <c r="D10" t="n">
-        <v>34.02246669067321</v>
+        <v>36.01541453029424</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.264712027248144</v>
+        <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>26.12136116689488</v>
       </c>
       <c r="D11" t="n">
-        <v>35.53926689373453</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -6518,10 +6518,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>26.68684784454105</v>
       </c>
       <c r="D12" t="n">
         <v>34.28066633689012</v>
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>34.86186097780424</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.20280516861837</v>
+        <v>23.96838845148163</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>34.10886048864694</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>18.99190933865455</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>32.6087499965578</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>30.58536797810513</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>25.97213551584937</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>31.29418982057133</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>13.23984953947248</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>13.4499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>96.83959354690535</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.463419127891162</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>83.96346518877557</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>6.530491736904767</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
